--- a/tame_output/ON/bt/strategyON_20241005.xlsx
+++ b/tame_output/ON/bt/strategyON_20241005.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.7%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,27 +1140,27 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.7%</t>
+          <t>-204.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -49000,10 +49000,10 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.794928205343332</v>
+        <v>-5.682280398885275</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.50185987140754</v>
+        <v>1.546918993990763</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6086779126578541</v>
@@ -49023,10 +49023,10 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.813146672340941</v>
+        <v>-5.700498865882883</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.494110847951429</v>
+        <v>1.539169970534652</v>
       </c>
       <c r="F2064" t="n">
         <v>0.5835714754020119</v>
@@ -49046,10 +49046,10 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.77446323699701</v>
+        <v>-5.661815430538953</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.52945861493932</v>
+        <v>1.574517737522543</v>
       </c>
       <c r="F2065" t="n">
         <v>0.5835714754020119</v>
@@ -49069,10 +49069,10 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.668428241791701</v>
+        <v>-5.555780435333643</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.555573313546172</v>
+        <v>1.600632436129395</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5835714754020119</v>
@@ -49092,10 +49092,10 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.485216578658606</v>
+        <v>-5.372568772200548</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.631288928263456</v>
+        <v>1.676348050846679</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5835714754020119</v>
@@ -49115,10 +49115,10 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.413495131644755</v>
+        <v>-5.300847325186697</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.642921913148373</v>
+        <v>1.687981035731596</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6552929224158626</v>
@@ -49138,10 +49138,10 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.391122106037049</v>
+        <v>-5.278474299578991</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.598786869312627</v>
+        <v>1.643845991895851</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6665486735287641</v>
@@ -49161,10 +49161,10 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.424138401947793</v>
+        <v>-5.311490595489736</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.770778555833684</v>
+        <v>1.815837678416908</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5971112968620125</v>
@@ -49184,10 +49184,10 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.412610766298185</v>
+        <v>-5.299962959840127</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.767310835921777</v>
+        <v>1.812369958505</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6561119550633749</v>
@@ -49207,10 +49207,10 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.509952267640553</v>
+        <v>-5.397304461182496</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.732042347906618</v>
+        <v>1.777101470489841</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6116917728978866</v>
@@ -49230,10 +49230,10 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.59580829698052</v>
+        <v>-5.483160490522462</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.69895101836347</v>
+        <v>1.744010140946693</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5693157036717515</v>
@@ -49253,10 +49253,10 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.604645094396639</v>
+        <v>-5.491997287938582</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.677835501217524</v>
+        <v>1.722894623800747</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5618735310304008</v>
@@ -49276,10 +49276,10 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.696027656962098</v>
+        <v>-5.58337985050404</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.65144698723639</v>
+        <v>1.696506109819613</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5253086463110561</v>
@@ -49299,10 +49299,10 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.684320938975092</v>
+        <v>-5.571673132517034</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.75825793225546</v>
+        <v>1.803317054838683</v>
       </c>
       <c r="F2076" t="n">
         <v>0.5370153642980625</v>
@@ -49322,10 +49322,10 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.755233012717369</v>
+        <v>-5.642585206259312</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.732925441489954</v>
+        <v>1.777984564073177</v>
       </c>
       <c r="F2077" t="n">
         <v>0.5370153642980625</v>
@@ -49345,10 +49345,10 @@
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.765549110883721</v>
+        <v>-5.652901304425664</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.729617827955678</v>
+        <v>1.774676950538901</v>
       </c>
       <c r="F2078" t="n">
         <v>0.5370153642980625</v>
@@ -49368,10 +49368,10 @@
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.765455142866348</v>
+        <v>-5.652807336408292</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.728834082074717</v>
+        <v>1.77389320465794</v>
       </c>
       <c r="F2079" t="n">
         <v>0.5373852256453805</v>
@@ -49391,10 +49391,10 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.909056306889734</v>
+        <v>-5.796408500431677</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.665625602409717</v>
+        <v>1.710684724992939</v>
       </c>
       <c r="F2080" t="n">
         <v>0.5373852256453805</v>
@@ -49414,10 +49414,10 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.908107883771695</v>
+        <v>-5.795460077313638</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.666004971656932</v>
+        <v>1.711064094240155</v>
       </c>
       <c r="F2081" t="n">
         <v>0.5373852256453805</v>
@@ -49437,10 +49437,10 @@
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.008377701730716</v>
+        <v>-5.895729895272659</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.638624652454416</v>
+        <v>1.683683775037638</v>
       </c>
       <c r="F2082" t="n">
         <v>0.5373852256453805</v>
@@ -49460,10 +49460,10 @@
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.002385454941904</v>
+        <v>-5.889737648483847</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.642967549594328</v>
+        <v>1.688026672177551</v>
       </c>
       <c r="F2083" t="n">
         <v>0.5373852256453805</v>
@@ -49483,10 +49483,10 @@
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.913827493811136</v>
+        <v>-5.80117968735308</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.672044870064404</v>
+        <v>1.717103992647627</v>
       </c>
       <c r="F2084" t="n">
         <v>0.5373852256453805</v>
@@ -49506,10 +49506,10 @@
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.896068416308062</v>
+        <v>-5.783420609850006</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.678457178504629</v>
+        <v>1.723516301087852</v>
       </c>
       <c r="F2085" t="n">
         <v>0.5373852256453805</v>
@@ -49529,10 +49529,10 @@
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.796438265258995</v>
+        <v>-5.683790458800938</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.731091424832843</v>
+        <v>1.776150547416066</v>
       </c>
       <c r="F2086" t="n">
         <v>0.637015376694448</v>
@@ -49552,10 +49552,10 @@
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.845837773948006</v>
+        <v>-5.733189967489949</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.900485886855965</v>
+        <v>1.945545009439188</v>
       </c>
       <c r="F2087" t="n">
         <v>0.6472742101261927</v>
@@ -49575,10 +49575,10 @@
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.63915330030563</v>
+        <v>-5.526505493847573</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.970348349415778</v>
+        <v>2.015407471999</v>
       </c>
       <c r="F2088" t="n">
         <v>0.8539586837685683</v>
@@ -49598,10 +49598,10 @@
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.673310195303156</v>
+        <v>-5.560662388845099</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.958687105070872</v>
+        <v>2.003746227654095</v>
       </c>
       <c r="F2089" t="n">
         <v>0.7703749142277558</v>
@@ -49621,10 +49621,10 @@
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.580720716241699</v>
+        <v>-5.468072909783642</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.349220010685122</v>
+        <v>2.394279133268345</v>
       </c>
       <c r="F2090" t="n">
         <v>0.7703749142277558</v>
@@ -49644,10 +49644,10 @@
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.653881320014844</v>
+        <v>-5.541233513556787</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.324518880742968</v>
+        <v>2.369578003326191</v>
       </c>
       <c r="F2091" t="n">
         <v>0.7423537141935128</v>
@@ -49667,10 +49667,10 @@
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.601665010218502</v>
+        <v>-5.489017203760445</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.395235345985033</v>
+        <v>2.440294468568255</v>
       </c>
       <c r="F2092" t="n">
         <v>0.7423537141935128</v>
@@ -49690,10 +49690,10 @@
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.549157682708008</v>
+        <v>-5.436509876249951</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.425052247199242</v>
+        <v>2.470111369782464</v>
       </c>
       <c r="F2093" t="n">
         <v>0.7948610417040077</v>
@@ -49713,10 +49713,10 @@
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.563913006908148</v>
+        <v>-5.451265200450091</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.414787701558382</v>
+        <v>2.459846824141605</v>
       </c>
       <c r="F2094" t="n">
         <v>0.7948610417040077</v>
@@ -49736,10 +49736,10 @@
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.514448383538237</v>
+        <v>-5.40180057708018</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.425498054322627</v>
+        <v>2.470557176905849</v>
       </c>
       <c r="F2095" t="n">
         <v>0.8443256650739194</v>
@@ -49759,10 +49759,10 @@
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.351340391384621</v>
+        <v>-5.238692584926564</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.487148918899007</v>
+        <v>2.53220804148223</v>
       </c>
       <c r="F2096" t="n">
         <v>1.007433657227535</v>
@@ -49782,10 +49782,10 @@
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.330697300583394</v>
+        <v>-5.218049494125337</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.504453191910626</v>
+        <v>2.549512314493849</v>
       </c>
       <c r="F2097" t="n">
         <v>1.007433657227535</v>
@@ -49805,10 +49805,10 @@
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.393405217057952</v>
+        <v>-5.280757410599895</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.480227490306925</v>
+        <v>2.525286612890147</v>
       </c>
       <c r="F2098" t="n">
         <v>0.9447257407529769</v>
@@ -49828,10 +49828,10 @@
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.345397093214259</v>
+        <v>-5.232749286756202</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.462340156634754</v>
+        <v>2.507399279217977</v>
       </c>
       <c r="F2099" t="n">
         <v>0.9447257407529769</v>
@@ -49851,10 +49851,10 @@
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.266571436030668</v>
+        <v>-5.153923629572612</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.497802673066141</v>
+        <v>2.542861795649364</v>
       </c>
       <c r="F2100" t="n">
         <v>1.023551397936567</v>
@@ -49874,10 +49874,10 @@
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.074636634776795</v>
+        <v>-4.961988828318738</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.569475686174727</v>
+        <v>2.61453480875795</v>
       </c>
       <c r="F2101" t="n">
         <v>1.023551397936567</v>
@@ -49897,10 +49897,10 @@
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.956463256758868</v>
+        <v>-4.843815450300811</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.612098946770993</v>
+        <v>2.657158069354216</v>
       </c>
       <c r="F2102" t="n">
         <v>1.141724775954495</v>
@@ -49920,10 +49920,10 @@
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.86761613989937</v>
+        <v>-4.754968333441314</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.676726386377819</v>
+        <v>2.721785508961042</v>
       </c>
       <c r="F2103" t="n">
         <v>1.230571892813992</v>
@@ -49943,10 +49943,10 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.840567102206117</v>
+        <v>-4.72791929574806</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.681106224466298</v>
+        <v>2.726165347049521</v>
       </c>
       <c r="F2104" t="n">
         <v>1.257620930507246</v>
@@ -49966,10 +49966,10 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.846600382392887</v>
+        <v>-4.73395257593483</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.67869291239159</v>
+        <v>2.723752034974813</v>
       </c>
       <c r="F2105" t="n">
         <v>1.257620930507246</v>
@@ -49989,10 +49989,10 @@
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.898452157966048</v>
+        <v>-4.785804351507991</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.661590369304737</v>
+        <v>2.70664949188796</v>
       </c>
       <c r="F2106" t="n">
         <v>1.205769154934085</v>
@@ -50006,16 +50006,16 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.783858569524919</v>
+        <v>3.901561043225941</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.928087114576122</v>
+        <v>-4.928494955187283</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.613228133844545</v>
+        <v>2.61306499760008</v>
       </c>
       <c r="F2107" t="n">
         <v>1.205769154934085</v>

--- a/tame_output/ON/bt/strategyON_20241005.xlsx
+++ b/tame_output/ON/bt/strategyON_20241005.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>420.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.4%</t>
+          <t>-653.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,27 +1140,27 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-114.9%</t>
+          <t>-114.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.2%</t>
+          <t>-205.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-103.4%</t>
+          <t>-100.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.0%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>101.5%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>86.4%</t>
         </is>
       </c>
     </row>
@@ -48517,16 +48517,16 @@
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.015182006923757</v>
+        <v>-5.011828080452537</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.44178890412125</v>
+        <v>1.443130474709738</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.5713971633852764</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.775188108296968</v>
+        <v>3.791056429235666</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.959851419021994</v>
+        <v>-4.956497492550774</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.498888075894013</v>
+        <v>1.500229646482501</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.6267277512870385</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.843353397650084</v>
+        <v>3.859221718588782</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.947797292109032</v>
+        <v>-4.944443365637811</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.497396294560636</v>
+        <v>1.498737865149124</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6123346766355037</v>
+        <v>0.6387818782000013</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.844272441699299</v>
+        <v>3.860140762637998</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.025152782237001</v>
+        <v>-5.02179885576578</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.468334728693584</v>
+        <v>1.469676299282072</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5349791865075343</v>
+        <v>0.5614263880720319</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.799739777806653</v>
+        <v>3.815608098745352</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.957104219545471</v>
+        <v>-4.953750293074251</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.508405179648078</v>
+        <v>1.509746750236567</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6294749507635617</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.853419941299454</v>
+        <v>3.869288262238152</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.188704612714972</v>
+        <v>-5.185350686243751</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.435967692553872</v>
+        <v>1.437309263142361</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6294749507635617</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.873622611473048</v>
+        <v>3.889490932411746</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.238756158244191</v>
+        <v>-5.235402231772971</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.399553310409066</v>
+        <v>1.400894880997555</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6294749507635617</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.85722884753993</v>
+        <v>3.873097168478628</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.413862990820636</v>
+        <v>-5.410509064349416</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.289762490971955</v>
+        <v>1.291104061560443</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6294749507635617</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.817480761133397</v>
+        <v>3.833349082072095</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.217762837390113</v>
+        <v>-5.214408910918893</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.375225171341104</v>
+        <v>1.376566741929592</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.799127902629587</v>
+        <v>0.8255751041940846</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.94216347218865</v>
+        <v>3.958031793127349</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.064737445276829</v>
+        <v>-5.061383518805608</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.535606327759323</v>
+        <v>1.536947898347811</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.9786004963073688</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.133149707029525</v>
+        <v>4.149018027968223</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.093044759150099</v>
+        <v>-5.089690832678879</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.711749627118307</v>
+        <v>1.713091197706795</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.9786004963073688</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.320615931937818</v>
+        <v>4.336484252876517</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.259637984263621</v>
+        <v>-5.256284057792401</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.614515288426981</v>
+        <v>1.615856859015469</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8120072711938464</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.190062948223787</v>
+        <v>4.205931269162486</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.236602190902055</v>
+        <v>-5.233248264430835</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.627406008433325</v>
+        <v>1.628747579021813</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8120072711938464</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.193739350885505</v>
+        <v>4.209607671824203</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.207356210446359</v>
+        <v>-5.204002283975139</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.636722455739099</v>
+        <v>1.638064026327587</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8120072711938464</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.191357406009</v>
+        <v>4.207225726947699</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.31428175832421</v>
+        <v>-5.31092783185299</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.591245475745593</v>
+        <v>1.592587046334081</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6786345217514974</v>
+        <v>0.7050817233159951</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.124495316439925</v>
+        <v>4.140363637378623</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.459300316831459</v>
+        <v>-5.455946390360238</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.534666854485928</v>
+        <v>1.536008425074416</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5336159632442489</v>
+        <v>0.5600631648087465</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.038912983478809</v>
+        <v>4.054781304417508</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.577642082616176</v>
+        <v>-5.574288156144956</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.587261387429794</v>
+        <v>1.588602958018282</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5707492033716366</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.145255845874297</v>
+        <v>4.161124166812995</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.629052504936884</v>
+        <v>-5.625698578465664</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.56448291562745</v>
+        <v>1.565824486215938</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5707492033716366</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.143041543000235</v>
+        <v>4.158909863938934</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.708471956144636</v>
+        <v>-5.705118029673415</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.532618263218639</v>
+        <v>1.533959833807127</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5707492033716366</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.142944671074525</v>
+        <v>4.158812992013223</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.803934954061853</v>
+        <v>-5.800581027590633</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.494426957609794</v>
+        <v>1.495768528198283</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5707492033716366</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.142938564632567</v>
+        <v>4.158806885571266</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.739559043211139</v>
+        <v>-5.736205116739918</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.518273718512691</v>
+        <v>1.519615289101179</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.6351251142223517</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.179660507705607</v>
+        <v>4.195528828644306</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.682280398885275</v>
+        <v>-5.791574278872112</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.546918993990763</v>
+        <v>1.503201441996028</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.6351251142223517</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.185394325453334</v>
+        <v>4.201262646392032</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.700498865882883</v>
+        <v>-5.80979274586972</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.539169970534652</v>
+        <v>1.495452418539918</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6100186769665096</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.169868826442761</v>
+        <v>4.18573714738146</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.661815430538953</v>
+        <v>-5.77110931052579</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.574517737522543</v>
+        <v>1.530800185527808</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6100186769665096</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.18974321929308</v>
+        <v>4.205611540231779</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.555780435333643</v>
+        <v>-5.665074315320481</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.600632436129395</v>
+        <v>1.55691488413466</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6100186769665096</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.173443919817807</v>
+        <v>4.189312240756506</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.372568772200548</v>
+        <v>-5.481862652187385</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.676348050846679</v>
+        <v>1.632630498851944</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6100186769665096</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.175874869281854</v>
+        <v>4.191743190220552</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.300847325186697</v>
+        <v>-5.410141205173534</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.687981035731596</v>
+        <v>1.644263483736861</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6552929224158626</v>
+        <v>0.6817401239803602</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.201852143569541</v>
+        <v>4.21772046450824</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.278474299578991</v>
+        <v>-5.387768179565828</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.643845991895851</v>
+        <v>1.600128439901115</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6665486735287641</v>
+        <v>0.6929958750932618</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.155521340158454</v>
+        <v>4.171389661097152</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.311490595489736</v>
+        <v>-5.420784475476573</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.815837678416908</v>
+        <v>1.772120126422173</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5971112968620125</v>
+        <v>0.6235584984265101</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.299057119043757</v>
+        <v>4.314925439982456</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.299962959840127</v>
+        <v>-5.409256839826964</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.812369958505</v>
+        <v>1.768652406510265</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6561119550633749</v>
+        <v>0.6825591566278726</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.326378739792824</v>
+        <v>4.342247060731522</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.397304461182496</v>
+        <v>-5.506598341169333</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.777101470489841</v>
+        <v>1.733383918495106</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6116917728978866</v>
+        <v>0.6381389744623842</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.303394743015319</v>
+        <v>4.319263063954018</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.483160490522462</v>
+        <v>-5.5924543705093</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.744010140946693</v>
+        <v>1.700292588951958</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5693157036717515</v>
+        <v>0.5957629052362492</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.279220183672477</v>
+        <v>4.295088504611176</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.491997287938582</v>
+        <v>-5.601291167925419</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.722894623800747</v>
+        <v>1.679177071806012</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.5883207325948985</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.257174081908168</v>
+        <v>4.273042402846867</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.58337985050404</v>
+        <v>-5.692673730490878</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.696506109819613</v>
+        <v>1.652788557824878</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.5517558478755538</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.245399662121611</v>
+        <v>4.26126798306031</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.571673132517034</v>
+        <v>-5.680967012503872</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.803317054838683</v>
+        <v>1.759599502843948</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5634625658625602</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.354551950738083</v>
+        <v>4.370420271676782</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.642585206259312</v>
+        <v>-5.751879086246149</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.777984564073177</v>
+        <v>1.734267012078443</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5634625658625602</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.357584289469488</v>
+        <v>4.373452610408187</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.652901304425664</v>
+        <v>-5.762195184412501</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.774676950538901</v>
+        <v>1.730959398544166</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5634625658625602</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.358403115201752</v>
+        <v>4.374271436140451</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.652807336408292</v>
+        <v>-5.762101216395128</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.77389320465794</v>
+        <v>1.730175652663205</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5638324272098781</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.357803698922233</v>
+        <v>4.373672019860932</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.796408500431677</v>
+        <v>-5.905702380418513</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.710684724992939</v>
+        <v>1.666967172998205</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5638324272098781</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.352035684866586</v>
+        <v>4.367904005805285</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.795460077313638</v>
+        <v>-5.904753957300475</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.711064094240155</v>
+        <v>1.66734654224542</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5638324272098781</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.352035684866586</v>
+        <v>4.367904005805285</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.895729895272659</v>
+        <v>-6.005023775259495</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.683683775037638</v>
+        <v>1.639966223042904</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5638324272098781</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.364763292847678</v>
+        <v>4.380631613786377</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.889737648483847</v>
+        <v>-5.999031528470684</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.688026672177551</v>
+        <v>1.644309120182816</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5638324272098781</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.366709291272066</v>
+        <v>4.382577612210765</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.80117968735308</v>
+        <v>-5.910473567339916</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.717103992647627</v>
+        <v>1.673386440652892</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5638324272098781</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.360363427289835</v>
+        <v>4.376231748228534</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.783420609850006</v>
+        <v>-5.892714489836842</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.723516301087852</v>
+        <v>1.679798749093118</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5638324272098781</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.359672104728831</v>
+        <v>4.37554042566753</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.683790458800938</v>
+        <v>-5.793084338787774</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.776150547416066</v>
+        <v>1.732432995421331</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.6634625782589456</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.432232381266858</v>
+        <v>4.448100702205557</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.733189967489949</v>
+        <v>-5.842483847476785</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.945545009439188</v>
+        <v>1.901827457444453</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.6737214116906903</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.627541946824631</v>
+        <v>4.64341026776333</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.526505493847573</v>
+        <v>-5.635799373834409</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.015407471999</v>
+        <v>1.971689920004266</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.880405885333066</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.738741304112919</v>
+        <v>4.754609625051617</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.560662388845099</v>
+        <v>-5.669956268831935</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.003746227654095</v>
+        <v>1.96002867565936</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.7968221157922535</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.690592556042536</v>
+        <v>4.706460876981235</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.468072909783642</v>
+        <v>-5.577366789770479</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.394279133268345</v>
+        <v>2.35056158127361</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.7968221157922535</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.044089670032204</v>
+        <v>5.059957990970902</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.541233513556787</v>
+        <v>-5.650527393543624</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.369578003326191</v>
+        <v>2.325860451331457</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7688009157580105</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.031840061578762</v>
+        <v>5.04770838251746</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.489017203760445</v>
+        <v>-5.598311083747282</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.440294468568255</v>
+        <v>2.396576916573521</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7688009157580105</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.081670002902289</v>
+        <v>5.097538323840988</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.436509876249951</v>
+        <v>-5.545803756236787</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.470111369782464</v>
+        <v>2.42639381778773</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7948610417040077</v>
+        <v>0.8213082432685054</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.121988369618597</v>
+        <v>5.137856690557296</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.451265200450091</v>
+        <v>-5.560559080436928</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.459846824141605</v>
+        <v>2.41612927214687</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7948610417040077</v>
+        <v>0.8213082432685054</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.117625953657794</v>
+        <v>5.133494274596493</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.40180057708018</v>
+        <v>-5.511094457067016</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.470557176905849</v>
+        <v>2.426839624911115</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8443256650739194</v>
+        <v>0.870772866638417</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.138229231096021</v>
+        <v>5.154097552034719</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.238692584926564</v>
+        <v>-5.347986464913401</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.53220804148223</v>
+        <v>2.488490489487496</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.007433657227535</v>
+        <v>1.033880858792032</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.232501694103124</v>
+        <v>5.248370015041823</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.218049494125337</v>
+        <v>-5.327343374112173</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.549512314493849</v>
+        <v>2.505794762499115</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.007433657227535</v>
+        <v>1.033880858792032</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.241548730794253</v>
+        <v>5.257417051732951</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.280757410599895</v>
+        <v>-5.390051290586731</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.525286612890147</v>
+        <v>2.481569060895413</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9447257407529769</v>
+        <v>0.9711729423174745</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.20478144589564</v>
+        <v>5.220649766834338</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.232749286756202</v>
+        <v>-5.342043166743038</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.507399279217977</v>
+        <v>2.463681727223242</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9447257407529769</v>
+        <v>0.9711729423174745</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.167690862685992</v>
+        <v>5.18355918362469</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.153923629572612</v>
+        <v>-5.263217509559448</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.542861795649364</v>
+        <v>2.499144243654629</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.023551397936567</v>
+        <v>1.049998599501065</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.218918510554097</v>
+        <v>5.234786831492795</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.961988828318738</v>
+        <v>-5.071282708305574</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.61453480875795</v>
+        <v>2.570817256763215</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.023551397936567</v>
+        <v>1.049998599501065</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.213817603161134</v>
+        <v>5.229685924099832</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.843815450300811</v>
+        <v>-4.953109330287647</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.657158069354216</v>
+        <v>2.613440517359481</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.141724775954495</v>
+        <v>1.168171977518992</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.280075539360985</v>
+        <v>5.295943860299684</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.754968333441314</v>
+        <v>-4.86426221342815</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.721785508961042</v>
+        <v>2.678067956966308</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.230571892813992</v>
+        <v>1.25701909437849</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.362472402339711</v>
+        <v>5.378340723278409</v>
       </c>
     </row>
     <row r="2104">
@@ -49943,16 +49943,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.72791929574806</v>
+        <v>-4.837213175734896</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.726165347049521</v>
+        <v>2.682447795054786</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.257620930507246</v>
+        <v>1.284068132071744</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.37226204796684</v>
+        <v>5.388130368905538</v>
       </c>
     </row>
     <row r="2105">
@@ -49966,16 +49966,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.73395257593483</v>
+        <v>-4.843246455921666</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.723752034974813</v>
+        <v>2.680034482980078</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.257620930507246</v>
+        <v>1.284068132071744</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.37226204796684</v>
+        <v>5.388130368905538</v>
       </c>
     </row>
     <row r="2106">
@@ -49989,16 +49989,16 @@
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.785804351507991</v>
+        <v>-4.895098231494828</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.70664949188796</v>
+        <v>2.662931939893226</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.205769154934085</v>
+        <v>1.232216356498582</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.344789149765356</v>
+        <v>5.360657470704054</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.901561043225941</v>
+        <v>3.785666385807866</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.928494955187283</v>
+        <v>-4.922155677626654</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.61306499760008</v>
+        <v>2.615600708624332</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.205769154934085</v>
+        <v>1.232216356498582</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.308280896949193</v>
+        <v>5.324149217887891</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241005.xlsx
+++ b/tame_output/ON/bt/strategyON_20241005.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-34.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.7%</t>
+          <t>421.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-653.8%</t>
+          <t>-649.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-114.7%</t>
+          <t>-112.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-205.0%</t>
+          <t>-205.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-100.8%</t>
+          <t>-98.5%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>87.8%</t>
         </is>
       </c>
     </row>
@@ -48517,16 +48517,16 @@
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.011828080452537</v>
+        <v>-5.015182006923757</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.443130474709738</v>
+        <v>1.44178890412125</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5713971633852764</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.791056429235666</v>
+        <v>3.775188108296968</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.956497492550774</v>
+        <v>-4.910391599821662</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.500229646482501</v>
+        <v>1.518672003574146</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6267277512870385</v>
+        <v>0.6497403689228733</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.859221718588782</v>
+        <v>3.873029289170283</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.944443365637811</v>
+        <v>-4.898337472908699</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.498737865149124</v>
+        <v>1.517180222240769</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6387818782000013</v>
+        <v>0.6617944958358362</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.860140762637998</v>
+        <v>3.873948333219499</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.02179885576578</v>
+        <v>-4.975692963036669</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.469676299282072</v>
+        <v>1.488118656373717</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5614263880720319</v>
+        <v>0.5844390057078668</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.815608098745352</v>
+        <v>3.829415669326853</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.953750293074251</v>
+        <v>-4.907644400345139</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.509746750236567</v>
+        <v>1.528189107328211</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6294749507635617</v>
+        <v>0.6524875683993966</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.869288262238152</v>
+        <v>3.883095832819653</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.185350686243751</v>
+        <v>-5.139244793514639</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.437309263142361</v>
+        <v>1.455751620234005</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6294749507635617</v>
+        <v>0.6524875683993966</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.889490932411746</v>
+        <v>3.903298502993247</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.235402231772971</v>
+        <v>-5.189296339043858</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.400894880997555</v>
+        <v>1.4193372380892</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6294749507635617</v>
+        <v>0.6524875683993966</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.873097168478628</v>
+        <v>3.886904739060129</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.410509064349416</v>
+        <v>-5.364403171620303</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.291104061560443</v>
+        <v>1.309546418652089</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6294749507635617</v>
+        <v>0.6524875683993966</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.833349082072095</v>
+        <v>3.847156652653596</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.214408910918893</v>
+        <v>-5.16830301818978</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.376566741929592</v>
+        <v>1.395009099021238</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8255751041940846</v>
+        <v>0.8485877218299195</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.958031793127349</v>
+        <v>3.97183936370885</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.061383518805608</v>
+        <v>-5.015277626076496</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.536947898347811</v>
+        <v>1.555390255439456</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9786004963073688</v>
+        <v>1.001613113943204</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.149018027968223</v>
+        <v>4.162825598549724</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.089690832678879</v>
+        <v>-5.043584939949766</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.713091197706795</v>
+        <v>1.73153355479844</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9786004963073688</v>
+        <v>1.001613113943204</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.336484252876517</v>
+        <v>4.350291823458017</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.256284057792401</v>
+        <v>-5.210178165063288</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.615856859015469</v>
+        <v>1.634299216107114</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8120072711938464</v>
+        <v>0.8350198888296811</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.205931269162486</v>
+        <v>4.219738839743986</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.233248264430835</v>
+        <v>-5.187142371701722</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.628747579021813</v>
+        <v>1.647189936113458</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8120072711938464</v>
+        <v>0.8350198888296811</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.209607671824203</v>
+        <v>4.223415242405704</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.204002283975139</v>
+        <v>-5.157896391246026</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.638064026327587</v>
+        <v>1.656506383419232</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8120072711938464</v>
+        <v>0.8350198888296811</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.207225726947699</v>
+        <v>4.2210332975292</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.31092783185299</v>
+        <v>-5.264821939123877</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.592587046334081</v>
+        <v>1.611029403425727</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7050817233159951</v>
+        <v>0.7280943409518298</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.140363637378623</v>
+        <v>4.154171207960124</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.455946390360238</v>
+        <v>-5.409840497631126</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.536008425074416</v>
+        <v>1.554450782166061</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5600631648087465</v>
+        <v>0.5830757824445812</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.054781304417508</v>
+        <v>4.068588874999008</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.574288156144956</v>
+        <v>-5.528182263415843</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.588602958018282</v>
+        <v>1.607045315109927</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5707492033716366</v>
+        <v>0.5937618210074713</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.161124166812995</v>
+        <v>4.174931737394496</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.625698578465664</v>
+        <v>-5.579592685736551</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.565824486215938</v>
+        <v>1.584266843307583</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5707492033716366</v>
+        <v>0.5937618210074713</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.158909863938934</v>
+        <v>4.172717434520435</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.705118029673415</v>
+        <v>-5.659012136944303</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.533959833807127</v>
+        <v>1.552402190898772</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5707492033716366</v>
+        <v>0.5937618210074713</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.158812992013223</v>
+        <v>4.172620562594724</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.800581027590633</v>
+        <v>-5.75447513486152</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.495768528198283</v>
+        <v>1.514210885289928</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5707492033716366</v>
+        <v>0.5937618210074713</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.158806885571266</v>
+        <v>4.172614456152767</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.736205116739918</v>
+        <v>-5.690099224010805</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.519615289101179</v>
+        <v>1.538057646192824</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6351251142223517</v>
+        <v>0.6581377318581865</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.195528828644306</v>
+        <v>4.209336399225807</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.791574278872112</v>
+        <v>-5.745468386142999</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.503201441996028</v>
+        <v>1.521643799087673</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6351251142223517</v>
+        <v>0.6581377318581865</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.201262646392032</v>
+        <v>4.215070216973533</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.80979274586972</v>
+        <v>-5.763686853140608</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.495452418539918</v>
+        <v>1.513894775631563</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6100186769665096</v>
+        <v>0.6330312946023443</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.18573714738146</v>
+        <v>4.199544717962961</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.77110931052579</v>
+        <v>-5.725003417796677</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.530800185527808</v>
+        <v>1.549242542619453</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6100186769665096</v>
+        <v>0.6330312946023443</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.205611540231779</v>
+        <v>4.219419110813279</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.665074315320481</v>
+        <v>-5.618968422591368</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.55691488413466</v>
+        <v>1.575357241226305</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6100186769665096</v>
+        <v>0.6330312946023443</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.189312240756506</v>
+        <v>4.203119811338007</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.481862652187385</v>
+        <v>-5.435756759458273</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.632630498851944</v>
+        <v>1.651072855943589</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6100186769665096</v>
+        <v>0.6330312946023443</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.191743190220552</v>
+        <v>4.205550760802053</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.410141205173534</v>
+        <v>-5.364035312444422</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.644263483736861</v>
+        <v>1.662705840828506</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6817401239803602</v>
+        <v>0.7047527416161949</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.21772046450824</v>
+        <v>4.23152803508974</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.387768179565828</v>
+        <v>-5.341662286836716</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.600128439901115</v>
+        <v>1.618570796992761</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6929958750932618</v>
+        <v>0.7160084927290965</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.171389661097152</v>
+        <v>4.185197231678653</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.420784475476573</v>
+        <v>-5.37467858274746</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.772120126422173</v>
+        <v>1.790562483513818</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6235584984265101</v>
+        <v>0.6465711160623449</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.314925439982456</v>
+        <v>4.328733010563957</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.409256839826964</v>
+        <v>-5.363150947097852</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.768652406510265</v>
+        <v>1.78709476360191</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6825591566278726</v>
+        <v>0.7055717742637073</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.342247060731522</v>
+        <v>4.356054631313024</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.506598341169333</v>
+        <v>-5.46049244844022</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.733383918495106</v>
+        <v>1.751826275586752</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6381389744623842</v>
+        <v>0.6611515920982189</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.319263063954018</v>
+        <v>4.333070634535519</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.5924543705093</v>
+        <v>-5.546348477780187</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.700292588951958</v>
+        <v>1.718734946043603</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5957629052362492</v>
+        <v>0.6187755228720839</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.295088504611176</v>
+        <v>4.308896075192676</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.601291167925419</v>
+        <v>-5.555185275196306</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.679177071806012</v>
+        <v>1.697619428897657</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5883207325948985</v>
+        <v>0.6113333502307332</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.273042402846867</v>
+        <v>4.286849973428367</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.692673730490878</v>
+        <v>-5.646567837761765</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.652788557824878</v>
+        <v>1.671230914916523</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5517558478755538</v>
+        <v>0.5747684655113885</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.26126798306031</v>
+        <v>4.27507555364181</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.680967012503872</v>
+        <v>-5.634861119774759</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.759599502843948</v>
+        <v>1.778041859935593</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5634625658625602</v>
+        <v>0.5864751834983949</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.370420271676782</v>
+        <v>4.384227842258282</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.751879086246149</v>
+        <v>-5.705773193517036</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.734267012078443</v>
+        <v>1.752709369170088</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5634625658625602</v>
+        <v>0.5864751834983949</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.373452610408187</v>
+        <v>4.387260180989687</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.762195184412501</v>
+        <v>-5.716089291683388</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.730959398544166</v>
+        <v>1.749401755635811</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5634625658625602</v>
+        <v>0.5864751834983949</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.374271436140451</v>
+        <v>4.388079006721951</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.762101216395128</v>
+        <v>-5.715995323666015</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.730175652663205</v>
+        <v>1.74861800975485</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5638324272098781</v>
+        <v>0.5868450448457129</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.373672019860932</v>
+        <v>4.387479590442432</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.905702380418513</v>
+        <v>-5.859596487689401</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.666967172998205</v>
+        <v>1.68540953008985</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5638324272098781</v>
+        <v>0.5868450448457129</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.367904005805285</v>
+        <v>4.381711576386786</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.904753957300475</v>
+        <v>-5.858648064571362</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.66734654224542</v>
+        <v>1.685788899337065</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5638324272098781</v>
+        <v>0.5868450448457129</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.367904005805285</v>
+        <v>4.381711576386786</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.005023775259495</v>
+        <v>-5.958917882530383</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.639966223042904</v>
+        <v>1.658408580134549</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5638324272098781</v>
+        <v>0.5868450448457129</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.380631613786377</v>
+        <v>4.394439184367878</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.999031528470684</v>
+        <v>-5.952925635741571</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.644309120182816</v>
+        <v>1.662751477274461</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5638324272098781</v>
+        <v>0.5868450448457129</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.382577612210765</v>
+        <v>4.396385182792265</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.910473567339916</v>
+        <v>-5.864367674610803</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.673386440652892</v>
+        <v>1.691828797744537</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5638324272098781</v>
+        <v>0.5868450448457129</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.376231748228534</v>
+        <v>4.390039318810034</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.892714489836842</v>
+        <v>-5.846608597107729</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.679798749093118</v>
+        <v>1.698241106184763</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5638324272098781</v>
+        <v>0.5868450448457129</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.37554042566753</v>
+        <v>4.38934799624903</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.793084338787774</v>
+        <v>-5.746978446058661</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.732432995421331</v>
+        <v>1.750875352512976</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6634625782589456</v>
+        <v>0.6864751958947803</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.448100702205557</v>
+        <v>4.461908272787057</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.842483847476785</v>
+        <v>-5.796377954747673</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.901827457444453</v>
+        <v>1.920269814536098</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6737214116906903</v>
+        <v>0.6967340293265251</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.64341026776333</v>
+        <v>4.657217838344831</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.635799373834409</v>
+        <v>-5.589693481105297</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.971689920004266</v>
+        <v>1.990132277095911</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.880405885333066</v>
+        <v>0.9034185029689007</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.754609625051617</v>
+        <v>4.768417195633118</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.669956268831935</v>
+        <v>-5.623850376102823</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.96002867565936</v>
+        <v>1.978471032751005</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7968221157922535</v>
+        <v>0.8198347334280882</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.706460876981235</v>
+        <v>4.720268447562736</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.577366789770479</v>
+        <v>-5.531260897041366</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.35056158127361</v>
+        <v>2.369003938365255</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7968221157922535</v>
+        <v>0.8198347334280882</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.059957990970902</v>
+        <v>5.073765561552403</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.650527393543624</v>
+        <v>-5.604421500814511</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.325860451331457</v>
+        <v>2.344302808423102</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7688009157580105</v>
+        <v>0.7918135333938452</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.04770838251746</v>
+        <v>5.061515953098962</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.598311083747282</v>
+        <v>-5.552205191018169</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.396576916573521</v>
+        <v>2.415019273665166</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7688009157580105</v>
+        <v>0.7918135333938452</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.097538323840988</v>
+        <v>5.111345894422489</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.545803756236787</v>
+        <v>-5.499697863507675</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.42639381778773</v>
+        <v>2.444836174879375</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8213082432685054</v>
+        <v>0.8443208609043401</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.137856690557296</v>
+        <v>5.151664261138797</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.560559080436928</v>
+        <v>-5.514453187707815</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.41612927214687</v>
+        <v>2.434571629238515</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8213082432685054</v>
+        <v>0.8443208609043401</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.133494274596493</v>
+        <v>5.147301845177994</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.511094457067016</v>
+        <v>-5.464988564337903</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.426839624911115</v>
+        <v>2.44528198200276</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.870772866638417</v>
+        <v>0.8937854842742518</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.154097552034719</v>
+        <v>5.16790512261622</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.347986464913401</v>
+        <v>-5.301880572184288</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.488490489487496</v>
+        <v>2.506932846579141</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.033880858792032</v>
+        <v>1.056893476427867</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.248370015041823</v>
+        <v>5.262177585623324</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.327343374112173</v>
+        <v>-5.28123748138306</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.505794762499115</v>
+        <v>2.52423711959076</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.033880858792032</v>
+        <v>1.056893476427867</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.257417051732951</v>
+        <v>5.271224622314453</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.390051290586731</v>
+        <v>-5.343945397857619</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.481569060895413</v>
+        <v>2.500011417987058</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9711729423174745</v>
+        <v>0.9941855599533094</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.220649766834338</v>
+        <v>5.234457337415839</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.342043166743038</v>
+        <v>-5.295937274013926</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.463681727223242</v>
+        <v>2.482124084314887</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9711729423174745</v>
+        <v>0.9941855599533094</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.18355918362469</v>
+        <v>5.197366754206191</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.263217509559448</v>
+        <v>-5.217111616830335</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.499144243654629</v>
+        <v>2.517586600746274</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.049998599501065</v>
+        <v>1.0730112171369</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.234786831492795</v>
+        <v>5.248594402074296</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.071282708305574</v>
+        <v>-5.025176815576462</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.570817256763215</v>
+        <v>2.58925961385486</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.049998599501065</v>
+        <v>1.0730112171369</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.229685924099832</v>
+        <v>5.243493494681333</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.953109330287647</v>
+        <v>-4.907003437558535</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.613440517359481</v>
+        <v>2.631882874451127</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.168171977518992</v>
+        <v>1.191184595154827</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.295943860299684</v>
+        <v>5.309751430881184</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.86426221342815</v>
+        <v>-4.818156320699037</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.678067956966308</v>
+        <v>2.696510314057952</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.25701909437849</v>
+        <v>1.280031712014325</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.378340723278409</v>
+        <v>5.39214829385991</v>
       </c>
     </row>
     <row r="2104">
@@ -49943,16 +49943,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.837213175734896</v>
+        <v>-4.791107283005783</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.682447795054786</v>
+        <v>2.700890152146431</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.284068132071744</v>
+        <v>1.307080749707578</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.388130368905538</v>
+        <v>5.401937939487039</v>
       </c>
     </row>
     <row r="2105">
@@ -49966,16 +49966,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.843246455921666</v>
+        <v>-4.797140563192554</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.680034482980078</v>
+        <v>2.698476840071723</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.284068132071744</v>
+        <v>1.307080749707578</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.388130368905538</v>
+        <v>5.401937939487039</v>
       </c>
     </row>
     <row r="2106">
@@ -49989,16 +49989,16 @@
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.895098231494828</v>
+        <v>-4.848992338765715</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.662931939893226</v>
+        <v>2.68137429698487</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.232216356498582</v>
+        <v>1.255228974134417</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.360657470704054</v>
+        <v>5.374465041285555</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.785666385807866</v>
+        <v>3.819004755892254</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.922155677626654</v>
+        <v>-4.876049784897542</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.615600708624332</v>
+        <v>2.634043065715977</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.232216356498582</v>
+        <v>1.255228974134417</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.324149217887891</v>
+        <v>5.337956788469392</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241005.xlsx
+++ b/tame_output/ON/bt/strategyON_20241005.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.9%</t>
+          <t>105.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>146.9%</t>
+          <t>156.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-649.2%</t>
+          <t>-652.2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-112.8%</t>
+          <t>-114.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-205.3%</t>
+          <t>-204.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-98.5%</t>
+          <t>-101.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>21.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2107"/>
+  <dimension ref="A1:G2108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48540,16 +48540,16 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.910391599821662</v>
+        <v>-4.959851419021994</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.518672003574146</v>
+        <v>1.498888075894013</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6497403689228733</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.873029289170283</v>
+        <v>3.843353397650084</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.898337472908699</v>
+        <v>-4.928864257453274</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.517180222240769</v>
+        <v>1.504969508422939</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6617944958358362</v>
+        <v>0.6312677112912612</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.873948333219499</v>
+        <v>3.855632262492754</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.975692963036669</v>
+        <v>-5.006219747581243</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.488118656373717</v>
+        <v>1.475907942555887</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5844390057078668</v>
+        <v>0.5539122211632919</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.829415669326853</v>
+        <v>3.811099598600108</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.907644400345139</v>
+        <v>-4.938171184889713</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.528189107328211</v>
+        <v>1.515978393510382</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6524875683993966</v>
+        <v>0.6219607838548217</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.883095832819653</v>
+        <v>3.864779762092908</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.139244793514639</v>
+        <v>-5.169771578059214</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.455751620234005</v>
+        <v>1.443540906416175</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6524875683993966</v>
+        <v>0.6219607838548217</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.903298502993247</v>
+        <v>3.884982432266503</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.189296339043858</v>
+        <v>-5.219823123588434</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.4193372380892</v>
+        <v>1.40712652427137</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6524875683993966</v>
+        <v>0.6219607838548217</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.886904739060129</v>
+        <v>3.868588668333384</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.364403171620303</v>
+        <v>-5.394929956164878</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.309546418652089</v>
+        <v>1.297335704834258</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6524875683993966</v>
+        <v>0.6219607838548217</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.847156652653596</v>
+        <v>3.828840581926851</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.16830301818978</v>
+        <v>-5.198829802734355</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.395009099021238</v>
+        <v>1.382798385203408</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8485877218299195</v>
+        <v>0.8180609372853446</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.97183936370885</v>
+        <v>3.953523292982105</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.015277626076496</v>
+        <v>-5.045804410621071</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.555390255439456</v>
+        <v>1.543179541621626</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.001613113943204</v>
+        <v>0.9710863293986287</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.162825598549724</v>
+        <v>4.144509527822979</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.043584939949766</v>
+        <v>-5.074111724494341</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.73153355479844</v>
+        <v>1.71932284098061</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.001613113943204</v>
+        <v>0.9710863293986287</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.350291823458017</v>
+        <v>4.331975752731272</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.210178165063288</v>
+        <v>-5.240704949607863</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.634299216107114</v>
+        <v>1.622088502289284</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8350198888296811</v>
+        <v>0.8044931042851062</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.219738839743986</v>
+        <v>4.201422769017242</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.187142371701722</v>
+        <v>-5.217669156246298</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.647189936113458</v>
+        <v>1.634979222295628</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8350198888296811</v>
+        <v>0.8044931042851062</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.223415242405704</v>
+        <v>4.20509917167896</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.157896391246026</v>
+        <v>-5.188423175790601</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.656506383419232</v>
+        <v>1.644295669601402</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8350198888296811</v>
+        <v>0.8044931042851062</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.2210332975292</v>
+        <v>4.202717226802454</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.264821939123877</v>
+        <v>-5.295348723668452</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.611029403425727</v>
+        <v>1.598818689607897</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7280943409518298</v>
+        <v>0.6975675564072549</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.154171207960124</v>
+        <v>4.135855137233379</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.409840497631126</v>
+        <v>-5.440367282175701</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.554450782166061</v>
+        <v>1.542240068348232</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5830757824445812</v>
+        <v>0.5525489979000063</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.068588874999008</v>
+        <v>4.050272804272264</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.528182263415843</v>
+        <v>-5.558709047960418</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.607045315109927</v>
+        <v>1.594834601292098</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5937618210074713</v>
+        <v>0.5632350364628964</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.174931737394496</v>
+        <v>4.156615666667751</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.579592685736551</v>
+        <v>-5.610119470281126</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.584266843307583</v>
+        <v>1.572056129489753</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5937618210074713</v>
+        <v>0.5632350364628964</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.172717434520435</v>
+        <v>4.15440136379369</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.659012136944303</v>
+        <v>-5.689538921488878</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.552402190898772</v>
+        <v>1.540191477080942</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5937618210074713</v>
+        <v>0.5632350364628964</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.172620562594724</v>
+        <v>4.154304491867979</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.75447513486152</v>
+        <v>-5.785001919406096</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.514210885289928</v>
+        <v>1.502000171472098</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5937618210074713</v>
+        <v>0.5632350364628964</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.172614456152767</v>
+        <v>4.154298385426022</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.690099224010805</v>
+        <v>-5.720626008555381</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.538057646192824</v>
+        <v>1.525846932374994</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6581377318581865</v>
+        <v>0.6276109473136116</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.209336399225807</v>
+        <v>4.191020328499062</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.745468386142999</v>
+        <v>-5.775995170687574</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.521643799087673</v>
+        <v>1.509433085269844</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6581377318581865</v>
+        <v>0.6276109473136116</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.215070216973533</v>
+        <v>4.196754146246788</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.763686853140608</v>
+        <v>-5.794213637685183</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.513894775631563</v>
+        <v>1.501684061813732</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6330312946023443</v>
+        <v>0.6025045100577694</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.199544717962961</v>
+        <v>4.181228647236216</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.725003417796677</v>
+        <v>-5.755530202341252</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.549242542619453</v>
+        <v>1.537031828801623</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6330312946023443</v>
+        <v>0.6025045100577694</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.219419110813279</v>
+        <v>4.201103040086534</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.618968422591368</v>
+        <v>-5.649495207135943</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.575357241226305</v>
+        <v>1.563146527408475</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6330312946023443</v>
+        <v>0.6025045100577694</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.203119811338007</v>
+        <v>4.184803740611262</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.435756759458273</v>
+        <v>-5.466283544002848</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.651072855943589</v>
+        <v>1.638862142125759</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6330312946023443</v>
+        <v>0.6025045100577694</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.205550760802053</v>
+        <v>4.187234690075308</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.364035312444422</v>
+        <v>-5.394562096988997</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.662705840828506</v>
+        <v>1.650495127010676</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7047527416161949</v>
+        <v>0.67422595707162</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.23152803508974</v>
+        <v>4.213211964362995</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.341662286836716</v>
+        <v>-5.372189071381291</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.618570796992761</v>
+        <v>1.606360083174931</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7160084927290965</v>
+        <v>0.6854817081845216</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.185197231678653</v>
+        <v>4.166881160951908</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.37467858274746</v>
+        <v>-5.405205367292035</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.790562483513818</v>
+        <v>1.778351769695988</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6465711160623449</v>
+        <v>0.6160443315177699</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.328733010563957</v>
+        <v>4.310416939837213</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.363150947097852</v>
+        <v>-5.393677731642427</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.78709476360191</v>
+        <v>1.77488404978408</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7055717742637073</v>
+        <v>0.6750449897191324</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.356054631313024</v>
+        <v>4.337738560586279</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.46049244844022</v>
+        <v>-5.491019232984796</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.751826275586752</v>
+        <v>1.739615561768921</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6611515920982189</v>
+        <v>0.630624807553644</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.333070634535519</v>
+        <v>4.314754563808775</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.546348477780187</v>
+        <v>-5.576875262324762</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.718734946043603</v>
+        <v>1.706524232225773</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6187755228720839</v>
+        <v>0.588248738327509</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.308896075192676</v>
+        <v>4.290580004465931</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.555185275196306</v>
+        <v>-5.585712059740882</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.697619428897657</v>
+        <v>1.685408715079827</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6113333502307332</v>
+        <v>0.5808065656861583</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.286849973428367</v>
+        <v>4.268533902701622</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.646567837761765</v>
+        <v>-5.67709462230634</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.671230914916523</v>
+        <v>1.659020201098693</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5747684655113885</v>
+        <v>0.5442416809668136</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.27507555364181</v>
+        <v>4.256759482915065</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.634861119774759</v>
+        <v>-5.665387904319334</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.778041859935593</v>
+        <v>1.765831146117764</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5864751834983949</v>
+        <v>0.55594839895382</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.384227842258282</v>
+        <v>4.365911771531537</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.705773193517036</v>
+        <v>-5.736299978061611</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.752709369170088</v>
+        <v>1.740498655352257</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5864751834983949</v>
+        <v>0.55594839895382</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.387260180989687</v>
+        <v>4.368944110262942</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.716089291683388</v>
+        <v>-5.746616076227963</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.749401755635811</v>
+        <v>1.737191041817981</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5864751834983949</v>
+        <v>0.55594839895382</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.388079006721951</v>
+        <v>4.369762935995206</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.715995323666015</v>
+        <v>-5.74652210821059</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.74861800975485</v>
+        <v>1.73640729593702</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5868450448457129</v>
+        <v>0.556318260301138</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.387479590442432</v>
+        <v>4.369163519715687</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.859596487689401</v>
+        <v>-5.890123272233976</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.68540953008985</v>
+        <v>1.673198816272019</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5868450448457129</v>
+        <v>0.556318260301138</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.381711576386786</v>
+        <v>4.363395505660041</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.858648064571362</v>
+        <v>-5.889174849115937</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.685788899337065</v>
+        <v>1.673578185519235</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5868450448457129</v>
+        <v>0.556318260301138</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.381711576386786</v>
+        <v>4.363395505660041</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.958917882530383</v>
+        <v>-5.989444667074958</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.658408580134549</v>
+        <v>1.646197866316719</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5868450448457129</v>
+        <v>0.556318260301138</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.394439184367878</v>
+        <v>4.376123113641133</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.952925635741571</v>
+        <v>-5.983452420286146</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.662751477274461</v>
+        <v>1.650540763456631</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5868450448457129</v>
+        <v>0.556318260301138</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.396385182792265</v>
+        <v>4.37806911206552</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.864367674610803</v>
+        <v>-5.894894459155378</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.691828797744537</v>
+        <v>1.679618083926707</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5868450448457129</v>
+        <v>0.556318260301138</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.390039318810034</v>
+        <v>4.371723248083289</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.846608597107729</v>
+        <v>-5.877135381652304</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.698241106184763</v>
+        <v>1.686030392366932</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5868450448457129</v>
+        <v>0.556318260301138</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.38934799624903</v>
+        <v>4.371031925522285</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.746978446058661</v>
+        <v>-5.777505230603237</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.750875352512976</v>
+        <v>1.738664638695147</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6864751958947803</v>
+        <v>0.6559484113502054</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.461908272787057</v>
+        <v>4.443592202060312</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.796377954747673</v>
+        <v>-5.826904739292248</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.920269814536098</v>
+        <v>1.908059100718269</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6967340293265251</v>
+        <v>0.6662072447819501</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.657217838344831</v>
+        <v>4.638901767618086</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.589693481105297</v>
+        <v>-5.620220265649872</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.990132277095911</v>
+        <v>1.977921563278081</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9034185029689007</v>
+        <v>0.8728917184243258</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.768417195633118</v>
+        <v>4.750101124906373</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.623850376102823</v>
+        <v>-5.654377160647398</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.978471032751005</v>
+        <v>1.966260318933176</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8198347334280882</v>
+        <v>0.7893079488835133</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.720268447562736</v>
+        <v>4.70195237683599</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.531260897041366</v>
+        <v>-5.561787681585941</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.369003938365255</v>
+        <v>2.356793224547425</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8198347334280882</v>
+        <v>0.7893079488835133</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.073765561552403</v>
+        <v>5.055449490825658</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.604421500814511</v>
+        <v>-5.634948285359086</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.344302808423102</v>
+        <v>2.332092094605271</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7918135333938452</v>
+        <v>0.7612867488492703</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.061515953098962</v>
+        <v>5.043199882372217</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.552205191018169</v>
+        <v>-5.582731975562744</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.415019273665166</v>
+        <v>2.402808559847336</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7918135333938452</v>
+        <v>0.7612867488492703</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.111345894422489</v>
+        <v>5.093029823695744</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.499697863507675</v>
+        <v>-5.53022464805225</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.444836174879375</v>
+        <v>2.432625461061545</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8443208609043401</v>
+        <v>0.8137940763597652</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.151664261138797</v>
+        <v>5.133348190412052</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.514453187707815</v>
+        <v>-5.54497997225239</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.434571629238515</v>
+        <v>2.422360915420685</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8443208609043401</v>
+        <v>0.8137940763597652</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.147301845177994</v>
+        <v>5.128985774451249</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.464988564337903</v>
+        <v>-5.495515348882479</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.44528198200276</v>
+        <v>2.43307126818493</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8937854842742518</v>
+        <v>0.8632586997296768</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.16790512261622</v>
+        <v>5.149589051889476</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.301880572184288</v>
+        <v>-5.332407356728863</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.506932846579141</v>
+        <v>2.49472213276131</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.056893476427867</v>
+        <v>1.026366691883292</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.262177585623324</v>
+        <v>5.243861514896579</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.28123748138306</v>
+        <v>-5.311764265927636</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.52423711959076</v>
+        <v>2.51202640577293</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.056893476427867</v>
+        <v>1.026366691883292</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.271224622314453</v>
+        <v>5.252908551587708</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.343945397857619</v>
+        <v>-5.374472182402194</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.500011417987058</v>
+        <v>2.487800704169228</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9941855599533094</v>
+        <v>0.9636587754087343</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.234457337415839</v>
+        <v>5.216141266689094</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.295937274013926</v>
+        <v>-5.326464058558501</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.482124084314887</v>
+        <v>2.469913370497058</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9941855599533094</v>
+        <v>0.9636587754087343</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.197366754206191</v>
+        <v>5.179050683479447</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.217111616830335</v>
+        <v>-5.24763840137491</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.517586600746274</v>
+        <v>2.505375886928444</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.0730112171369</v>
+        <v>1.042484432592325</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.248594402074296</v>
+        <v>5.230278331347551</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.025176815576462</v>
+        <v>-5.055703600121037</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.58925961385486</v>
+        <v>2.57704890003703</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.0730112171369</v>
+        <v>1.042484432592325</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.243493494681333</v>
+        <v>5.225177423954588</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.907003437558535</v>
+        <v>-4.93753022210311</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.631882874451127</v>
+        <v>2.619672160633296</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.191184595154827</v>
+        <v>1.160657810610252</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.309751430881184</v>
+        <v>5.291435360154439</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.818156320699037</v>
+        <v>-4.848683105243612</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.696510314057952</v>
+        <v>2.684299600240122</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.280031712014325</v>
+        <v>1.24950492746975</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.39214829385991</v>
+        <v>5.373832223133165</v>
       </c>
     </row>
     <row r="2104">
@@ -49943,16 +49943,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.791107283005783</v>
+        <v>-4.821634067550359</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.700890152146431</v>
+        <v>2.688679438328601</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.307080749707578</v>
+        <v>1.276553965163004</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.401937939487039</v>
+        <v>5.383621868760295</v>
       </c>
     </row>
     <row r="2105">
@@ -49966,16 +49966,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.797140563192554</v>
+        <v>-4.827667347737129</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.698476840071723</v>
+        <v>2.686266126253892</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.307080749707578</v>
+        <v>1.276553965163004</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.401937939487039</v>
+        <v>5.383621868760295</v>
       </c>
     </row>
     <row r="2106">
@@ -49989,16 +49989,16 @@
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.848992338765715</v>
+        <v>-4.87951912331029</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.68137429698487</v>
+        <v>2.669163583167041</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.255228974134417</v>
+        <v>1.224702189589842</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.374465041285555</v>
+        <v>5.35614897055881</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,45 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.819004755892254</v>
+        <v>3.830586986431404</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.876049784897542</v>
+        <v>-4.906576569442117</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.634043065715977</v>
+        <v>2.621832351898147</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.255228974134417</v>
+        <v>1.224702189589842</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.337956788469392</v>
+        <v>5.319640717742647</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="2" t="n">
+        <v>45570</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>3.824708578704786</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>4.682460243026613</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>-4.906576569442117</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>2.621832351898147</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>1.224702189589842</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>4.675524040012981</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241005.xlsx
+++ b/tame_output/ON/bt/strategyON_20241005.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>49.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>156.6%</t>
+          <t>147.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.2%</t>
+          <t>420.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-652.2%</t>
+          <t>-654.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-114.0%</t>
+          <t>-114.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.9%</t>
+          <t>-204.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-101.5%</t>
+          <t>-103.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
     </row>
@@ -48563,16 +48563,16 @@
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.928864257453274</v>
+        <v>-4.947797292109032</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.504969508422939</v>
+        <v>1.497396294560636</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6312677112912612</v>
+        <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.855632262492754</v>
+        <v>3.844272441699299</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.006219747581243</v>
+        <v>-5.025152782237001</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.475907942555887</v>
+        <v>1.468334728693584</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5539122211632919</v>
+        <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.811099598600108</v>
+        <v>3.799739777806653</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.938171184889713</v>
+        <v>-4.957104219545471</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.515978393510382</v>
+        <v>1.508405179648078</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6219607838548217</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.864779762092908</v>
+        <v>3.853419941299454</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.169771578059214</v>
+        <v>-5.188704612714972</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.443540906416175</v>
+        <v>1.435967692553872</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6219607838548217</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.884982432266503</v>
+        <v>3.873622611473048</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.219823123588434</v>
+        <v>-5.238756158244191</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.40712652427137</v>
+        <v>1.399553310409066</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6219607838548217</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.868588668333384</v>
+        <v>3.85722884753993</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.394929956164878</v>
+        <v>-5.413862990820636</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.297335704834258</v>
+        <v>1.289762490971955</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6219607838548217</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.828840581926851</v>
+        <v>3.817480761133397</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.198829802734355</v>
+        <v>-5.217762837390113</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.382798385203408</v>
+        <v>1.375225171341104</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8180609372853446</v>
+        <v>0.799127902629587</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.953523292982105</v>
+        <v>3.94216347218865</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.045804410621071</v>
+        <v>-5.064737445276829</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.543179541621626</v>
+        <v>1.535606327759323</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9710863293986287</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.144509527822979</v>
+        <v>4.133149707029525</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.074111724494341</v>
+        <v>-5.093044759150099</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.71932284098061</v>
+        <v>1.711749627118307</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9710863293986287</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.331975752731272</v>
+        <v>4.320615931937818</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.240704949607863</v>
+        <v>-5.259637984263621</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.622088502289284</v>
+        <v>1.614515288426981</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8044931042851062</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.201422769017242</v>
+        <v>4.190062948223787</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.217669156246298</v>
+        <v>-5.236602190902055</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.634979222295628</v>
+        <v>1.627406008433325</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8044931042851062</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.20509917167896</v>
+        <v>4.193739350885505</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.188423175790601</v>
+        <v>-5.207356210446359</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.644295669601402</v>
+        <v>1.636722455739099</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8044931042851062</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.202717226802454</v>
+        <v>4.191357406009</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.295348723668452</v>
+        <v>-5.31428175832421</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.598818689607897</v>
+        <v>1.591245475745593</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6975675564072549</v>
+        <v>0.6786345217514974</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.135855137233379</v>
+        <v>4.124495316439925</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.440367282175701</v>
+        <v>-5.459300316831459</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.542240068348232</v>
+        <v>1.534666854485928</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5525489979000063</v>
+        <v>0.5336159632442489</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.050272804272264</v>
+        <v>4.038912983478809</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.558709047960418</v>
+        <v>-5.577642082616176</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.594834601292098</v>
+        <v>1.587261387429794</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5632350364628964</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.156615666667751</v>
+        <v>4.145255845874297</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.610119470281126</v>
+        <v>-5.629052504936884</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.572056129489753</v>
+        <v>1.56448291562745</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5632350364628964</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.15440136379369</v>
+        <v>4.143041543000235</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.689538921488878</v>
+        <v>-5.708471956144636</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.540191477080942</v>
+        <v>1.532618263218639</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5632350364628964</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.154304491867979</v>
+        <v>4.142944671074525</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.785001919406096</v>
+        <v>-5.803934954061853</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.502000171472098</v>
+        <v>1.494426957609794</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5632350364628964</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.154298385426022</v>
+        <v>4.142938564632567</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.720626008555381</v>
+        <v>-5.739559043211139</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.525846932374994</v>
+        <v>1.518273718512691</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6276109473136116</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.191020328499062</v>
+        <v>4.179660507705607</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.775995170687574</v>
+        <v>-5.794928205343332</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.509433085269844</v>
+        <v>1.50185987140754</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6276109473136116</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.196754146246788</v>
+        <v>4.185394325453334</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.794213637685183</v>
+        <v>-5.813146672340941</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.501684061813732</v>
+        <v>1.494110847951429</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6025045100577694</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.181228647236216</v>
+        <v>4.169868826442761</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113693</v>
+        <v>3.790272500113694</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.755530202341252</v>
+        <v>-5.77446323699701</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.537031828801623</v>
+        <v>1.52945861493932</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6025045100577694</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.201103040086534</v>
+        <v>4.18974321929308</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.649495207135943</v>
+        <v>-5.668428241791701</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.563146527408475</v>
+        <v>1.555573313546172</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6025045100577694</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.184803740611262</v>
+        <v>4.173443919817807</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.466283544002848</v>
+        <v>-5.485216578658606</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.638862142125759</v>
+        <v>1.631288928263456</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6025045100577694</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.187234690075308</v>
+        <v>4.175874869281854</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.394562096988997</v>
+        <v>-5.413495131644755</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.650495127010676</v>
+        <v>1.642921913148373</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.67422595707162</v>
+        <v>0.6552929224158626</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.213211964362995</v>
+        <v>4.201852143569541</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.372189071381291</v>
+        <v>-5.391122106037049</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.606360083174931</v>
+        <v>1.598786869312627</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6854817081845216</v>
+        <v>0.6665486735287641</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.166881160951908</v>
+        <v>4.155521340158454</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.405205367292035</v>
+        <v>-5.424138401947793</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.778351769695988</v>
+        <v>1.770778555833684</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6160443315177699</v>
+        <v>0.5971112968620125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.310416939837213</v>
+        <v>4.299057119043757</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.393677731642427</v>
+        <v>-5.412610766298185</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.77488404978408</v>
+        <v>1.767310835921777</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6750449897191324</v>
+        <v>0.6561119550633749</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.337738560586279</v>
+        <v>4.326378739792824</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.491019232984796</v>
+        <v>-5.509952267640553</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.739615561768921</v>
+        <v>1.732042347906618</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.630624807553644</v>
+        <v>0.6116917728978866</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.314754563808775</v>
+        <v>4.303394743015319</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.576875262324762</v>
+        <v>-5.59580829698052</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.706524232225773</v>
+        <v>1.69895101836347</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.588248738327509</v>
+        <v>0.5693157036717515</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.290580004465931</v>
+        <v>4.279220183672477</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.920049963289927</v>
+        <v>3.918329447233319</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.585712059740882</v>
+        <v>-5.604645094396639</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.685408715079827</v>
+        <v>1.676114985160915</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5808065656861583</v>
+        <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.268533902701622</v>
+        <v>4.25545356585156</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667459</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.930214474334977</v>
+        <v>3.928493958278368</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.67709462230634</v>
+        <v>-5.696027656962098</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.659020201098693</v>
+        <v>1.649726471179781</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5442416809668136</v>
+        <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.256759482915065</v>
+        <v>4.243679146065002</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889197</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.032342732159245</v>
+        <v>4.030622216102635</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.665387904319334</v>
+        <v>-5.684320938975092</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.765831146117764</v>
+        <v>1.756537416198851</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.55594839895382</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.365911771531537</v>
+        <v>4.352831434681473</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.03537507089065</v>
+        <v>4.03365455483404</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.736299978061611</v>
+        <v>-5.755233012717369</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.740498655352257</v>
+        <v>1.731204925433345</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.55594839895382</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.368944110262942</v>
+        <v>4.355863773412878</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.036193896622915</v>
+        <v>4.034473380566305</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.746616076227963</v>
+        <v>-5.765549110883721</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.737191041817981</v>
+        <v>1.727897311899068</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.55594839895382</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.369762935995206</v>
+        <v>4.356682599145143</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762292</v>
+        <v>3.623960959762293</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.035372563535004</v>
+        <v>4.033652047478395</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.74652210821059</v>
+        <v>-5.765455142866348</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.73640729593702</v>
+        <v>1.727113566018107</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.556318260301138</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.369163519715687</v>
+        <v>4.356083182865623</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884084</v>
+        <v>3.800870306884086</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.029604549479358</v>
+        <v>4.027884033422748</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.890123272233976</v>
+        <v>-5.909056306889734</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.673198816272019</v>
+        <v>1.663905086353107</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.556318260301138</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.363395505660041</v>
+        <v>4.350315168809977</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.671015692129648</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.029604549479358</v>
+        <v>4.027884033422748</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.889174849115937</v>
+        <v>-5.908107883771695</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.673578185519235</v>
+        <v>1.664284455600322</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.556318260301138</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.363395505660041</v>
+        <v>4.350315168809977</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.904173816052351</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.04233215746045</v>
+        <v>4.04061164140384</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.989444667074958</v>
+        <v>-6.008377701730716</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.646197866316719</v>
+        <v>1.636904136397806</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.556318260301138</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.376123113641133</v>
+        <v>4.363042776791069</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.740179607813495</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.044278155884838</v>
+        <v>4.042557639828228</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.983452420286146</v>
+        <v>-6.002385454941904</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.650540763456631</v>
+        <v>1.641247033537719</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.556318260301138</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.37806911206552</v>
+        <v>4.364988775215457</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.765050796537944</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.037932291902607</v>
+        <v>4.036211775845997</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.894894459155378</v>
+        <v>-5.913827493811136</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.679618083926707</v>
+        <v>1.670324354007795</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.556318260301138</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.371723248083289</v>
+        <v>4.358642911233225</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.758409170771816</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.037240969341602</v>
+        <v>4.035520453284993</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.877135381652304</v>
+        <v>-5.896068416308062</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.686030392366932</v>
+        <v>1.67673666244802</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.556318260301138</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.371031925522285</v>
+        <v>4.357951588672221</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.801340597109721</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.050023155250189</v>
+        <v>4.048302639193579</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.777505230603237</v>
+        <v>-5.796438265258995</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.738664638695147</v>
+        <v>1.729370908776234</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6559484113502054</v>
+        <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.443592202060312</v>
+        <v>4.430511865210248</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.798465546843996</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.239177420748915</v>
+        <v>4.237456904692306</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.826904739292248</v>
+        <v>-5.845837773948006</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.908059100718269</v>
+        <v>1.898765370799356</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6662072447819501</v>
+        <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.638901767618086</v>
+        <v>4.625821430768021</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.77218650835186</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.226366093851778</v>
+        <v>4.224645577795168</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.620220265649872</v>
+        <v>-5.63915330030563</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.977921563278081</v>
+        <v>1.968627833359168</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8728917184243258</v>
+        <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.750101124906373</v>
+        <v>4.737020788056309</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.76339283855127</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.228367607505882</v>
+        <v>4.226647091449273</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.654377160647398</v>
+        <v>-5.673310195303156</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.966260318933176</v>
+        <v>1.956966589014263</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7893079488835133</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.70195237683599</v>
+        <v>4.688872039985926</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.805590565041111</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.58186472149555</v>
+        <v>4.58014420543894</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.561787681585941</v>
+        <v>-5.580720716241699</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.356793224547425</v>
+        <v>2.347499494628513</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7893079488835133</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.055449490825658</v>
+        <v>5.042369153975594</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.832164354497403</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.586427833062654</v>
+        <v>4.584707317006044</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.634948285359086</v>
+        <v>-5.653881320014844</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.332092094605271</v>
+        <v>2.322798364686359</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7612867488492703</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.043199882372217</v>
+        <v>5.030119545522153</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.858310890492296</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.636257774386181</v>
+        <v>4.634537258329572</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.582731975562744</v>
+        <v>-5.601665010218502</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.402808559847336</v>
+        <v>2.393514829928423</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7612867488492703</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.093029823695744</v>
+        <v>5.079949486845679</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.844935596436478</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.645071744596192</v>
+        <v>4.643351228539583</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.53022464805225</v>
+        <v>-5.549157682708008</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.432625461061545</v>
+        <v>2.423331731142632</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8137940763597652</v>
+        <v>0.7948610417040077</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.133348190412052</v>
+        <v>5.120267853561987</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.848376866039487</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.640709328635389</v>
+        <v>4.63898881257878</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.54497997225239</v>
+        <v>-5.563913006908148</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.422360915420685</v>
+        <v>2.413067185501772</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8137940763597652</v>
+        <v>0.7948610417040077</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.128985774451249</v>
+        <v>5.115905437601184</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524482</v>
+        <v>3.868153115524483</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.631633832051669</v>
+        <v>4.62991331599506</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.495515348882479</v>
+        <v>-5.514448383538237</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.43307126818493</v>
+        <v>2.423777538266017</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8632586997296768</v>
+        <v>0.8443256650739194</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.149589051889476</v>
+        <v>5.136508715039412</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867955</v>
+        <v>3.849040239867957</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.628041499766604</v>
+        <v>4.626320983709994</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.332407356728863</v>
+        <v>-5.351340391384621</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.49472213276131</v>
+        <v>2.485428402842398</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.026366691883292</v>
+        <v>1.007433657227535</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.243861514896579</v>
+        <v>5.230781178046515</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232971</v>
+        <v>3.870204928232972</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.637088536457732</v>
+        <v>4.635368020401122</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.311764265927636</v>
+        <v>-5.330697300583394</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.51202640577293</v>
+        <v>2.502732675854017</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.026366691883292</v>
+        <v>1.007433657227535</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.252908551587708</v>
+        <v>5.239828214737643</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179674</v>
+        <v>3.855534437179675</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.637946001443853</v>
+        <v>4.636225485387244</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.374472182402194</v>
+        <v>-5.393405217057952</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.487800704169228</v>
+        <v>2.478506974250315</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9636587754087343</v>
+        <v>0.9447257407529769</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.216141266689094</v>
+        <v>5.20306092983903</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967721</v>
+        <v>3.884687848967722</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.600855418234206</v>
+        <v>4.599134902177596</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.326464058558501</v>
+        <v>-5.345397093214259</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.469913370497058</v>
+        <v>2.460619640578145</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9636587754087343</v>
+        <v>0.9447257407529769</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.179050683479447</v>
+        <v>5.165970346629383</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018612</v>
+        <v>3.895362357018613</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.604787671792156</v>
+        <v>4.603067155735546</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.24763840137491</v>
+        <v>-5.266571436030668</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.505375886928444</v>
+        <v>2.496082157009531</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.042484432592325</v>
+        <v>1.023551397936567</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.230278331347551</v>
+        <v>5.217197994497488</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075135</v>
+        <v>3.891610981075137</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.599686764399193</v>
+        <v>4.597966248342583</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.055703600121037</v>
+        <v>-5.074636634776795</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.57704890003703</v>
+        <v>2.567755170118117</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.042484432592325</v>
+        <v>1.023551397936567</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.225177423954588</v>
+        <v>5.212097087104524</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435445</v>
+        <v>3.872432493435447</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.595040673788288</v>
+        <v>4.593320157731679</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.93753022210311</v>
+        <v>-4.956463256758868</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.619672160633296</v>
+        <v>2.610378430714384</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.160657810610252</v>
+        <v>1.141724775954495</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.291435360154439</v>
+        <v>5.278355023304376</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917734</v>
+        <v>3.859571723917735</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.624129266651315</v>
+        <v>4.622408750594706</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.848683105243612</v>
+        <v>-4.86761613989937</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.684299600240122</v>
+        <v>2.675005870321209</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.24950492746975</v>
+        <v>1.230571892813992</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.373832223133165</v>
+        <v>5.360751886283102</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.82800627401364</v>
+        <v>3.828006274013642</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.617689489662492</v>
+        <v>4.615968973605883</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.821634067550359</v>
+        <v>-4.839208563505061</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.688679438328601</v>
+        <v>2.67992912389011</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.276553965163004</v>
+        <v>1.258979469208301</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.383621868760295</v>
+        <v>5.371356655130864</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.82398744526377</v>
+        <v>3.823987445263771</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.617689489662492</v>
+        <v>4.615968973605883</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.827667347737129</v>
+        <v>-4.845241843691832</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.686266126253892</v>
+        <v>2.677515811815402</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.276553965163004</v>
+        <v>1.258979469208301</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.383621868760295</v>
+        <v>5.371356655130864</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170844</v>
+        <v>3.815657203170845</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.621327656804905</v>
+        <v>4.619607140748295</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.87951912331029</v>
+        <v>-4.897093619264993</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.669163583167041</v>
+        <v>2.66041326872855</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.224702189589842</v>
+        <v>1.20712769363514</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.35614897055881</v>
+        <v>5.34388375692938</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431404</v>
+        <v>3.830586986431407</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.584819403988742</v>
+        <v>4.583098887932132</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.906576569442117</v>
+        <v>-4.92415106539682</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.621832351898147</v>
+        <v>2.613082037459656</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.224702189589842</v>
+        <v>1.20712769363514</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.319640717742647</v>
+        <v>5.307375504113216</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.824708578704786</v>
+        <v>3.771082919394444</v>
       </c>
       <c r="C2108" t="n">
-        <v>4.682460243026613</v>
+        <v>4.589117110459836</v>
       </c>
       <c r="D2108" t="n">
-        <v>-4.906576569442117</v>
+        <v>-4.92415106539682</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.621832351898147</v>
+        <v>2.613082037459656</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.224702189589842</v>
+        <v>1.20712769363514</v>
       </c>
       <c r="G2108" t="n">
-        <v>4.675524040012981</v>
+        <v>4.582180907446204</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241005.xlsx
+++ b/tame_output/ON/bt/strategyON_20241005.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.0%</t>
+          <t>101.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>147.3%</t>
+          <t>146.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.5%</t>
+          <t>420.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.0%</t>
+          <t>-656.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-114.9%</t>
+          <t>-115.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.7%</t>
+          <t>-204.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-103.3%</t>
+          <t>-101.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113694</v>
+        <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
@@ -49250,19 +49250,19 @@
         <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.918329447233319</v>
+        <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.604645094396639</v>
+        <v>-5.623373650793</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.676114985160915</v>
+        <v>1.670344078658979</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.5831852460522594</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.25545356585156</v>
+        <v>4.269961110921283</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667459</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.928493958278368</v>
+        <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.696027656962098</v>
+        <v>-5.714756213358458</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.649726471179781</v>
+        <v>1.643955564677845</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.5466203613329148</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.243679146065002</v>
+        <v>4.258186691134726</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889197</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.030622216102635</v>
+        <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.684320938975092</v>
+        <v>-5.703049495371452</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.756537416198851</v>
+        <v>1.750766509696916</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5583270793199212</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.352831434681473</v>
+        <v>4.367338979751198</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.03365455483404</v>
+        <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.755233012717369</v>
+        <v>-5.77396156911373</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.731204925433345</v>
+        <v>1.72543401893141</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5583270793199212</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.355863773412878</v>
+        <v>4.370371318482603</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.034473380566305</v>
+        <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.765549110883721</v>
+        <v>-5.784277667280082</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.727897311899068</v>
+        <v>1.722126405397133</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5583270793199212</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.356682599145143</v>
+        <v>4.371190144214867</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762293</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.033652047478395</v>
+        <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.765455142866348</v>
+        <v>-5.78418369926271</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.727113566018107</v>
+        <v>1.721342659516172</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5586969406672392</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.356083182865623</v>
+        <v>4.370590727935348</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.800870306884086</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.027884033422748</v>
+        <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.909056306889734</v>
+        <v>-5.927784863286095</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.663905086353107</v>
+        <v>1.658134179851172</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5586969406672392</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.350315168809977</v>
+        <v>4.364822713879701</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.671015692129648</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.027884033422748</v>
+        <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.908107883771695</v>
+        <v>-5.926836440168056</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.664284455600322</v>
+        <v>1.658513549098387</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5586969406672392</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.350315168809977</v>
+        <v>4.364822713879701</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.904173816052351</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.04061164140384</v>
+        <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.008377701730716</v>
+        <v>-6.027106258127077</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.636904136397806</v>
+        <v>1.631133229895871</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5586969406672392</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.363042776791069</v>
+        <v>4.377550321860793</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.740179607813495</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.042557639828228</v>
+        <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.002385454941904</v>
+        <v>-6.021114011338265</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.641247033537719</v>
+        <v>1.635476127035783</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5586969406672392</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.364988775215457</v>
+        <v>4.379496320285181</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.765050796537944</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.036211775845997</v>
+        <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.913827493811136</v>
+        <v>-5.932556050207498</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.670324354007795</v>
+        <v>1.66455344750586</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5586969406672392</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.358642911233225</v>
+        <v>4.37315045630295</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.758409170771816</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.035520453284993</v>
+        <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.896068416308062</v>
+        <v>-5.914796972704424</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.67673666244802</v>
+        <v>1.670965755946085</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5586969406672392</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.357951588672221</v>
+        <v>4.372459133741946</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.801340597109721</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.048302639193579</v>
+        <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.796438265258995</v>
+        <v>-5.815166821655356</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.729370908776234</v>
+        <v>1.723600002274299</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.6583270917163067</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.430511865210248</v>
+        <v>4.445019410279973</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.798465546843996</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.237456904692306</v>
+        <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.845837773948006</v>
+        <v>-5.864566330344367</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.898765370799356</v>
+        <v>1.892994464297421</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.6685859251480514</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.625821430768021</v>
+        <v>4.640328975837747</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.77218650835186</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.224645577795168</v>
+        <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.63915330030563</v>
+        <v>-5.657881856701991</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.968627833359168</v>
+        <v>1.962856926857233</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.875270398790427</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.737020788056309</v>
+        <v>4.751528333126034</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.76339283855127</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.226647091449273</v>
+        <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.673310195303156</v>
+        <v>-5.692038751699517</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.956966589014263</v>
+        <v>1.951195682512328</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.7916866292496145</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.688872039985926</v>
+        <v>4.703379585055652</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.805590565041111</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.58014420543894</v>
+        <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.580720716241699</v>
+        <v>-5.59944927263806</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.347499494628513</v>
+        <v>2.341728588126578</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.7916866292496145</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.042369153975594</v>
+        <v>5.056876699045318</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.832164354497403</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.584707317006044</v>
+        <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.653881320014844</v>
+        <v>-5.672609876411205</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.322798364686359</v>
+        <v>2.317027458184424</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7636654292153715</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.030119545522153</v>
+        <v>5.044627090591877</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.858310890492296</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.634537258329572</v>
+        <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.601665010218502</v>
+        <v>-5.620393566614863</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.393514829928423</v>
+        <v>2.387743923426488</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7636654292153715</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.079949486845679</v>
+        <v>5.094457031915405</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.844935596436478</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.643351228539583</v>
+        <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.549157682708008</v>
+        <v>-5.567886239104369</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.423331731142632</v>
+        <v>2.417560824640697</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7948610417040077</v>
+        <v>0.8161727567258664</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.120267853561987</v>
+        <v>5.134775398631713</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.848376866039487</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.63898881257878</v>
+        <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.563913006908148</v>
+        <v>-5.582641563304509</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.413067185501772</v>
+        <v>2.407296278999838</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7948610417040077</v>
+        <v>0.8161727567258664</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.115905437601184</v>
+        <v>5.13041298267091</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524483</v>
+        <v>3.868153115524482</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.62991331599506</v>
+        <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.514448383538237</v>
+        <v>-5.533176939934598</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.423777538266017</v>
+        <v>2.418006631764082</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8443256650739194</v>
+        <v>0.8656373800957781</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.136508715039412</v>
+        <v>5.151016260109136</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867957</v>
+        <v>3.849040239867955</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.626320983709994</v>
+        <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.351340391384621</v>
+        <v>-5.370068947780982</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.485428402842398</v>
+        <v>2.479657496340463</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.007433657227535</v>
+        <v>1.028745372249393</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.230781178046515</v>
+        <v>5.24528872311624</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232972</v>
+        <v>3.87020492823297</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.635368020401122</v>
+        <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.330697300583394</v>
+        <v>-5.349425856979755</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.502732675854017</v>
+        <v>2.496961769352082</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.007433657227535</v>
+        <v>1.028745372249393</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.239828214737643</v>
+        <v>5.254335759807368</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179675</v>
+        <v>3.855534437179673</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.636225485387244</v>
+        <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.393405217057952</v>
+        <v>-5.412133773454313</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.478506974250315</v>
+        <v>2.47273606774838</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9447257407529769</v>
+        <v>0.9660374557748356</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.20306092983903</v>
+        <v>5.217568474908755</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967722</v>
+        <v>3.884687848967721</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.599134902177596</v>
+        <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.345397093214259</v>
+        <v>-5.36412564961062</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.460619640578145</v>
+        <v>2.45484873407621</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9447257407529769</v>
+        <v>0.9660374557748356</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.165970346629383</v>
+        <v>5.180477891699107</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018613</v>
+        <v>3.895362357018612</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.603067155735546</v>
+        <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.266571436030668</v>
+        <v>-5.28529999242703</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.496082157009531</v>
+        <v>2.490311250507596</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.023551397936567</v>
+        <v>1.044863112958426</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.217197994497488</v>
+        <v>5.231705539567212</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075137</v>
+        <v>3.891610981075135</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.597966248342583</v>
+        <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.074636634776795</v>
+        <v>-5.093365191173156</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.567755170118117</v>
+        <v>2.561984263616182</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.023551397936567</v>
+        <v>1.044863112958426</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.212097087104524</v>
+        <v>5.226604632174249</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435447</v>
+        <v>3.872432493435445</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.593320157731679</v>
+        <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.956463256758868</v>
+        <v>-4.975191813155229</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.610378430714384</v>
+        <v>2.604607524212449</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.141724775954495</v>
+        <v>1.163036490976353</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.278355023304376</v>
+        <v>5.2928625683741</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917735</v>
+        <v>3.859571723917734</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.622408750594706</v>
+        <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.86761613989937</v>
+        <v>-4.886344696295732</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.675005870321209</v>
+        <v>2.669234963819274</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.230571892813992</v>
+        <v>1.251883607835851</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.360751886283102</v>
+        <v>5.375259431352826</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013642</v>
+        <v>3.82800627401364</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.615968973605883</v>
+        <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.839208563505061</v>
+        <v>-4.859295658602478</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.67992912389011</v>
+        <v>2.673614801907753</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.258979469208301</v>
+        <v>1.278932645529105</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.371356655130864</v>
+        <v>5.385049076979955</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263771</v>
+        <v>3.82398744526377</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.615968973605883</v>
+        <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.845241843691832</v>
+        <v>-4.865328938789248</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.677515811815402</v>
+        <v>2.671201489833045</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.258979469208301</v>
+        <v>1.278932645529105</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.371356655130864</v>
+        <v>5.385049076979955</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170845</v>
+        <v>3.815657203170844</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.619607140748295</v>
+        <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.897093619264993</v>
+        <v>-4.917180714362409</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.66041326872855</v>
+        <v>2.654098946746193</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.20712769363514</v>
+        <v>1.227080869955943</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.34388375692938</v>
+        <v>5.357576178778471</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431407</v>
+        <v>3.830586986431405</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.583098887932132</v>
+        <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.92415106539682</v>
+        <v>-4.944238160494236</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.613082037459656</v>
+        <v>2.606767715477299</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.20712769363514</v>
+        <v>1.227080869955943</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.307375504113216</v>
+        <v>5.321067925962308</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.771082919394444</v>
+        <v>3.759877169304604</v>
       </c>
       <c r="C2108" t="n">
-        <v>4.589117110459836</v>
+        <v>4.580457478197187</v>
       </c>
       <c r="D2108" t="n">
-        <v>-4.92415106539682</v>
+        <v>-4.944238160494236</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.613082037459656</v>
+        <v>2.606767715477299</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.20712769363514</v>
+        <v>1.227080869955943</v>
       </c>
       <c r="G2108" t="n">
-        <v>4.582180907446204</v>
+        <v>4.573521275183555</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241005.xlsx
+++ b/tame_output/ON/bt/strategyON_20241005.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.7%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>146.4%</t>
+          <t>139.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.4%</t>
+          <t>419.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-656.0%</t>
+          <t>-667.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-115.5%</t>
+          <t>-120.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.9%</t>
+          <t>-204.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-101.3%</t>
+          <t>-107.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -48655,10 +48655,10 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.238756158244191</v>
+        <v>-5.285126233616388</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.399553310409066</v>
+        <v>1.381005280260188</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6030277491990641</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.413862990820636</v>
+        <v>-5.460233066192833</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.289762490971955</v>
+        <v>1.271214460823077</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6030277491990641</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.217762837390113</v>
+        <v>-5.26413291276231</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.375225171341104</v>
+        <v>1.356677141192226</v>
       </c>
       <c r="F2050" t="n">
         <v>0.799127902629587</v>
@@ -48724,10 +48724,10 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.064737445276829</v>
+        <v>-5.111107520649026</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.535606327759323</v>
+        <v>1.517058297610444</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9521532947428711</v>
@@ -48747,10 +48747,10 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.093044759150099</v>
+        <v>-5.139414834522296</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.711749627118307</v>
+        <v>1.693201596969428</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9521532947428711</v>
@@ -48770,10 +48770,10 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.259637984263621</v>
+        <v>-5.306008059635818</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.614515288426981</v>
+        <v>1.595967258278102</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7855600696293488</v>
@@ -48793,10 +48793,10 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.236602190902055</v>
+        <v>-5.282972266274252</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.627406008433325</v>
+        <v>1.608857978284446</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7855600696293488</v>
@@ -48816,10 +48816,10 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.207356210446359</v>
+        <v>-5.253726285818556</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.636722455739099</v>
+        <v>1.61817442559022</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7855600696293488</v>
@@ -48839,10 +48839,10 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.31428175832421</v>
+        <v>-5.360651833696407</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.591245475745593</v>
+        <v>1.572697445596715</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6786345217514974</v>
@@ -48862,10 +48862,10 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.459300316831459</v>
+        <v>-5.505670392203656</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.534666854485928</v>
+        <v>1.516118824337049</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5336159632442489</v>
@@ -48885,10 +48885,10 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.577642082616176</v>
+        <v>-5.624012157988373</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.587261387429794</v>
+        <v>1.568713357280915</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5443020018071389</v>
@@ -48908,10 +48908,10 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.629052504936884</v>
+        <v>-5.675422580309081</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.56448291562745</v>
+        <v>1.545934885478571</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5443020018071389</v>
@@ -48931,10 +48931,10 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.708471956144636</v>
+        <v>-5.754842031516833</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.532618263218639</v>
+        <v>1.51407023306976</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5443020018071389</v>
@@ -48954,10 +48954,10 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.803934954061853</v>
+        <v>-5.85030502943405</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.494426957609794</v>
+        <v>1.475878927460916</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5443020018071389</v>
@@ -48977,10 +48977,10 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.739559043211139</v>
+        <v>-5.785929118583335</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.518273718512691</v>
+        <v>1.499725688363812</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6086779126578541</v>
@@ -49000,10 +49000,10 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.794928205343332</v>
+        <v>-5.841298280715529</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.50185987140754</v>
+        <v>1.483311841258661</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6086779126578541</v>
@@ -49023,10 +49023,10 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.813146672340941</v>
+        <v>-5.859516747713138</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.494110847951429</v>
+        <v>1.475562817802551</v>
       </c>
       <c r="F2064" t="n">
         <v>0.5835714754020119</v>
@@ -49046,10 +49046,10 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.77446323699701</v>
+        <v>-5.820833312369207</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.52945861493932</v>
+        <v>1.510910584790441</v>
       </c>
       <c r="F2065" t="n">
         <v>0.5835714754020119</v>
@@ -49069,10 +49069,10 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.668428241791701</v>
+        <v>-5.714798317163898</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.555573313546172</v>
+        <v>1.537025283397293</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5835714754020119</v>
@@ -49092,10 +49092,10 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.485216578658606</v>
+        <v>-5.531586654030803</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.631288928263456</v>
+        <v>1.612740898114577</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5835714754020119</v>
@@ -49115,10 +49115,10 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.413495131644755</v>
+        <v>-5.459865207016952</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.642921913148373</v>
+        <v>1.624373882999494</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6552929224158626</v>
@@ -49138,10 +49138,10 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.391122106037049</v>
+        <v>-5.437492181409246</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.598786869312627</v>
+        <v>1.580238839163749</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6665486735287641</v>
@@ -49161,10 +49161,10 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.424138401947793</v>
+        <v>-5.47050847731999</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.770778555833684</v>
+        <v>1.752230525684806</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5971112968620125</v>
@@ -49184,10 +49184,10 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.412610766298185</v>
+        <v>-5.458980841670382</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.767310835921777</v>
+        <v>1.748762805772898</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6561119550633749</v>
@@ -49207,10 +49207,10 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.509952267640553</v>
+        <v>-5.55632234301275</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.732042347906618</v>
+        <v>1.71349431775774</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6116917728978866</v>
@@ -49230,10 +49230,10 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.59580829698052</v>
+        <v>-5.642178372352717</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.69895101836347</v>
+        <v>1.680402988214591</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5693157036717515</v>
@@ -49253,16 +49253,16 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.623373650793</v>
+        <v>-5.651015169768836</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.670344078658979</v>
+        <v>1.659287471068645</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5831852460522594</v>
+        <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.269961110921283</v>
+        <v>4.257174081908168</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.714756213358458</v>
+        <v>-5.742397732334295</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.643955564677845</v>
+        <v>1.632898957087511</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5466203613329148</v>
+        <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.258186691134726</v>
+        <v>4.245399662121611</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.703049495371452</v>
+        <v>-5.730691014347289</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.750766509696916</v>
+        <v>1.739709902106581</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5583270793199212</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.367338979751198</v>
+        <v>4.354551950738083</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.77396156911373</v>
+        <v>-5.801603088089566</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.72543401893141</v>
+        <v>1.714377411341076</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5583270793199212</v>
+        <v>0.5117156656620966</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.370371318482603</v>
+        <v>4.342404470287908</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.784277667280082</v>
+        <v>-5.811919186255918</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.722126405397133</v>
+        <v>1.711069797806799</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5583270793199212</v>
+        <v>0.5117156656620966</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.371190144214867</v>
+        <v>4.343223296020173</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762293</v>
+        <v>3.623960959762292</v>
       </c>
       <c r="C2079" t="n">
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.78418369926271</v>
+        <v>-5.899233054837445</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.721342659516172</v>
+        <v>1.675322917286278</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5586969406672392</v>
+        <v>0.5017111854802323</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.370590727935348</v>
+        <v>4.336399274823144</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884086</v>
+        <v>3.800870306884084</v>
       </c>
       <c r="C2080" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.927784863286095</v>
+        <v>-6.04283421886083</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.658134179851172</v>
+        <v>1.612114437621278</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5586969406672392</v>
+        <v>0.5017111854802323</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.364822713879701</v>
+        <v>4.330631260767498</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.926836440168056</v>
+        <v>-6.041885795742791</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.658513549098387</v>
+        <v>1.612493806868494</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5586969406672392</v>
+        <v>0.5017111854802323</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.364822713879701</v>
+        <v>4.330631260767498</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.027106258127077</v>
+        <v>-6.142155613701812</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.631133229895871</v>
+        <v>1.585113487665977</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5586969406672392</v>
+        <v>0.5017111854802323</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.377550321860793</v>
+        <v>4.34335886874859</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.021114011338265</v>
+        <v>-6.136163366913</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.635476127035783</v>
+        <v>1.58945638480589</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5586969406672392</v>
+        <v>0.5017111854802323</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.379496320285181</v>
+        <v>4.345304867172977</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.932556050207498</v>
+        <v>-6.047605405782233</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.66455344750586</v>
+        <v>1.618533705275965</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5586969406672392</v>
+        <v>0.5017111854802323</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.37315045630295</v>
+        <v>4.338959003190746</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.914796972704424</v>
+        <v>-6.029846328279159</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.670965755946085</v>
+        <v>1.624946013716191</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5586969406672392</v>
+        <v>0.5017111854802323</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.372459133741946</v>
+        <v>4.338267680629742</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.815166821655356</v>
+        <v>-5.930216177230091</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.723600002274299</v>
+        <v>1.677580260044405</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6583270917163067</v>
+        <v>0.6013413365292998</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.445019410279973</v>
+        <v>4.410827957167769</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.864566330344367</v>
+        <v>-5.979615685919102</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.892994464297421</v>
+        <v>1.846974722067527</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6685859251480514</v>
+        <v>0.6116001699610445</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.640328975837747</v>
+        <v>4.606137522725542</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.657881856701991</v>
+        <v>-5.772931212276726</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.962856926857233</v>
+        <v>1.916837184627339</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.875270398790427</v>
+        <v>0.8182846436034201</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.751528333126034</v>
+        <v>4.71733688001383</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.692038751699517</v>
+        <v>-5.807088107274252</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.951195682512328</v>
+        <v>1.905175940282434</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7916866292496145</v>
+        <v>0.7347008740626076</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.703379585055652</v>
+        <v>4.669188131943447</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.59944927263806</v>
+        <v>-5.714498628212795</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.341728588126578</v>
+        <v>2.295708845896684</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7916866292496145</v>
+        <v>0.7347008740626076</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.056876699045318</v>
+        <v>5.022685245933115</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.672609876411205</v>
+        <v>-5.78765923198594</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.317027458184424</v>
+        <v>2.27100771595453</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7636654292153715</v>
+        <v>0.7066796740283645</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.044627090591877</v>
+        <v>5.010435637479673</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.620393566614863</v>
+        <v>-5.735442922189598</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.387743923426488</v>
+        <v>2.341724181196594</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7636654292153715</v>
+        <v>0.7066796740283645</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.094457031915405</v>
+        <v>5.0602655788032</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.567886239104369</v>
+        <v>-5.682935594679104</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.417560824640697</v>
+        <v>2.371541082410803</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8161727567258664</v>
+        <v>0.7591870015388594</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.134775398631713</v>
+        <v>5.100583945519508</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.582641563304509</v>
+        <v>-5.697690918879244</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.407296278999838</v>
+        <v>2.361276536769944</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8161727567258664</v>
+        <v>0.7591870015388594</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.13041298267091</v>
+        <v>5.096221529558705</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.533176939934598</v>
+        <v>-5.648226295509333</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.418006631764082</v>
+        <v>2.371986889534188</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8656373800957781</v>
+        <v>0.8086516249087711</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.151016260109136</v>
+        <v>5.116824806996932</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.370068947780982</v>
+        <v>-5.485118303355717</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.479657496340463</v>
+        <v>2.433637754110569</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.028745372249393</v>
+        <v>0.9717596170623863</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.24528872311624</v>
+        <v>5.211097270004036</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.87020492823297</v>
+        <v>3.870204928232971</v>
       </c>
       <c r="C2097" t="n">
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.349425856979755</v>
+        <v>-5.46447521255449</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.496961769352082</v>
+        <v>2.450942027122188</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.028745372249393</v>
+        <v>0.9717596170623863</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.254335759807368</v>
+        <v>5.220144306695164</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179673</v>
+        <v>3.855534437179674</v>
       </c>
       <c r="C2098" t="n">
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.412133773454313</v>
+        <v>-5.527183129029048</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.47273606774838</v>
+        <v>2.426716325518486</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9660374557748356</v>
+        <v>0.9090517005878286</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.217568474908755</v>
+        <v>5.18337702179655</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.36412564961062</v>
+        <v>-5.479175005185355</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.45484873407621</v>
+        <v>2.408828991846315</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9660374557748356</v>
+        <v>0.9090517005878286</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.180477891699107</v>
+        <v>5.146286438586903</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.28529999242703</v>
+        <v>-5.400349348001765</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.490311250507596</v>
+        <v>2.444291508277702</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.044863112958426</v>
+        <v>0.9878773577714191</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.231705539567212</v>
+        <v>5.197514086455008</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.093365191173156</v>
+        <v>-5.208414546747891</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.561984263616182</v>
+        <v>2.515964521386289</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.044863112958426</v>
+        <v>0.9878773577714191</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.226604632174249</v>
+        <v>5.192413179062044</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.975191813155229</v>
+        <v>-5.090241168729964</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.604607524212449</v>
+        <v>2.558587781982555</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.163036490976353</v>
+        <v>1.106050735789346</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.2928625683741</v>
+        <v>5.258671115261897</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.886344696295732</v>
+        <v>-5.001394051870466</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.669234963819274</v>
+        <v>2.623215221589381</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.251883607835851</v>
+        <v>1.194897852648844</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.375259431352826</v>
+        <v>5.341067978240622</v>
       </c>
     </row>
     <row r="2104">
@@ -49943,16 +49943,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.859295658602478</v>
+        <v>-4.974345014177213</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.673614801907753</v>
+        <v>2.627595059677859</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.278932645529105</v>
+        <v>1.221946890342098</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.385049076979955</v>
+        <v>5.350857623867752</v>
       </c>
     </row>
     <row r="2105">
@@ -49966,16 +49966,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.865328938789248</v>
+        <v>-4.980378294363983</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.671201489833045</v>
+        <v>2.625181747603151</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.278932645529105</v>
+        <v>1.221946890342098</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.385049076979955</v>
+        <v>5.350857623867752</v>
       </c>
     </row>
     <row r="2106">
@@ -49989,16 +49989,16 @@
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.917180714362409</v>
+        <v>-5.032230069937144</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.654098946746193</v>
+        <v>2.608079204516299</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.227080869955943</v>
+        <v>1.170095114768936</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.357576178778471</v>
+        <v>5.323384725666267</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431405</v>
+        <v>3.830586986431406</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.944238160494236</v>
+        <v>-5.059287516068971</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.606767715477299</v>
+        <v>2.560747973247405</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.227080869955943</v>
+        <v>1.170095114768936</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.321067925962308</v>
+        <v>5.286876472850103</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.759877169304604</v>
+        <v>3.702899209171088</v>
       </c>
       <c r="C2108" t="n">
-        <v>4.580457478197187</v>
+        <v>4.511075558311259</v>
       </c>
       <c r="D2108" t="n">
-        <v>-4.944238160494236</v>
+        <v>-5.059287516068971</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.606767715477299</v>
+        <v>2.560747973247405</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.227080869955943</v>
+        <v>1.170095114768936</v>
       </c>
       <c r="G2108" t="n">
-        <v>4.573521275183555</v>
+        <v>4.504139355297627</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241005.xlsx
+++ b/tame_output/ON/bt/strategyON_20241005.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>57.2%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>101.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>139.5%</t>
+          <t>146.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.6%</t>
+          <t>421.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-667.5%</t>
+          <t>-650.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-120.1%</t>
+          <t>-113.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.3%</t>
+          <t>-204.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-107.0%</t>
+          <t>-104.0%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>84.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2108"/>
+  <dimension ref="A1:G2107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48655,10 +48655,10 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.285126233616388</v>
+        <v>-5.238756158244191</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.381005280260188</v>
+        <v>1.399553310409066</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6030277491990641</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.460233066192833</v>
+        <v>-5.413862990820636</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.271214460823077</v>
+        <v>1.289762490971955</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6030277491990641</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.26413291276231</v>
+        <v>-5.217762837390113</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.356677141192226</v>
+        <v>1.375225171341104</v>
       </c>
       <c r="F2050" t="n">
         <v>0.799127902629587</v>
@@ -48724,10 +48724,10 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.111107520649026</v>
+        <v>-5.064737445276829</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.517058297610444</v>
+        <v>1.535606327759323</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9521532947428711</v>
@@ -48747,10 +48747,10 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.139414834522296</v>
+        <v>-5.093044759150099</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.693201596969428</v>
+        <v>1.711749627118307</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9521532947428711</v>
@@ -48770,10 +48770,10 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.306008059635818</v>
+        <v>-5.259637984263621</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.595967258278102</v>
+        <v>1.614515288426981</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7855600696293488</v>
@@ -48793,10 +48793,10 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.282972266274252</v>
+        <v>-5.236602190902055</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.608857978284446</v>
+        <v>1.627406008433325</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7855600696293488</v>
@@ -48816,10 +48816,10 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.253726285818556</v>
+        <v>-5.207356210446359</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.61817442559022</v>
+        <v>1.636722455739099</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7855600696293488</v>
@@ -48839,10 +48839,10 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.360651833696407</v>
+        <v>-5.31428175832421</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.572697445596715</v>
+        <v>1.591245475745593</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6786345217514974</v>
@@ -48862,10 +48862,10 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.505670392203656</v>
+        <v>-5.459300316831459</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.516118824337049</v>
+        <v>1.534666854485928</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5336159632442489</v>
@@ -48885,10 +48885,10 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.624012157988373</v>
+        <v>-5.577642082616176</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.568713357280915</v>
+        <v>1.587261387429794</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5443020018071389</v>
@@ -48908,10 +48908,10 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.675422580309081</v>
+        <v>-5.629052504936884</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.545934885478571</v>
+        <v>1.56448291562745</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5443020018071389</v>
@@ -48931,10 +48931,10 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.754842031516833</v>
+        <v>-5.708471956144636</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.51407023306976</v>
+        <v>1.532618263218639</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5443020018071389</v>
@@ -48954,10 +48954,10 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.85030502943405</v>
+        <v>-5.803934954061853</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.475878927460916</v>
+        <v>1.494426957609794</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5443020018071389</v>
@@ -48977,10 +48977,10 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.785929118583335</v>
+        <v>-5.739559043211139</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.499725688363812</v>
+        <v>1.518273718512691</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6086779126578541</v>
@@ -49000,10 +49000,10 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.841298280715529</v>
+        <v>-5.794928205343332</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.483311841258661</v>
+        <v>1.50185987140754</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6086779126578541</v>
@@ -49023,10 +49023,10 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.859516747713138</v>
+        <v>-5.813146672340941</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.475562817802551</v>
+        <v>1.494110847951429</v>
       </c>
       <c r="F2064" t="n">
         <v>0.5835714754020119</v>
@@ -49046,10 +49046,10 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.820833312369207</v>
+        <v>-5.77446323699701</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.510910584790441</v>
+        <v>1.52945861493932</v>
       </c>
       <c r="F2065" t="n">
         <v>0.5835714754020119</v>
@@ -49069,10 +49069,10 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.714798317163898</v>
+        <v>-5.668428241791701</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.537025283397293</v>
+        <v>1.555573313546172</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5835714754020119</v>
@@ -49092,10 +49092,10 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.531586654030803</v>
+        <v>-5.485216578658606</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.612740898114577</v>
+        <v>1.631288928263456</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5835714754020119</v>
@@ -49115,10 +49115,10 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.459865207016952</v>
+        <v>-5.413495131644755</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.624373882999494</v>
+        <v>1.642921913148373</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6552929224158626</v>
@@ -49138,10 +49138,10 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.437492181409246</v>
+        <v>-5.391122106037049</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.580238839163749</v>
+        <v>1.598786869312627</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6665486735287641</v>
@@ -49161,10 +49161,10 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.47050847731999</v>
+        <v>-5.424138401947793</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.752230525684806</v>
+        <v>1.770778555833684</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5971112968620125</v>
@@ -49184,10 +49184,10 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.458980841670382</v>
+        <v>-5.412610766298185</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.748762805772898</v>
+        <v>1.767310835921777</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6561119550633749</v>
@@ -49207,10 +49207,10 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.55632234301275</v>
+        <v>-5.509952267640553</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.71349431775774</v>
+        <v>1.732042347906618</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6116917728978866</v>
@@ -49230,10 +49230,10 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.642178372352717</v>
+        <v>-5.59580829698052</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.680402988214591</v>
+        <v>1.69895101836347</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5693157036717515</v>
@@ -49253,10 +49253,10 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.651015169768836</v>
+        <v>-5.604645094396639</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.659287471068645</v>
+        <v>1.677835501217524</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5618735310304008</v>
@@ -49276,10 +49276,10 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.742397732334295</v>
+        <v>-5.696027656962098</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.632898957087511</v>
+        <v>1.65144698723639</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5253086463110561</v>
@@ -49299,10 +49299,10 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.730691014347289</v>
+        <v>-5.684320938975092</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.739709902106581</v>
+        <v>1.75825793225546</v>
       </c>
       <c r="F2076" t="n">
         <v>0.5370153642980625</v>
@@ -49322,16 +49322,16 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.801603088089566</v>
+        <v>-5.755233012717369</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.714377411341076</v>
+        <v>1.732925441489954</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5117156656620966</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.342404470287908</v>
+        <v>4.357584289469488</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.811919186255918</v>
+        <v>-5.765549110883721</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.711069797806799</v>
+        <v>1.729617827955678</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5117156656620966</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.343223296020173</v>
+        <v>4.358403115201752</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762292</v>
+        <v>3.770053391710332</v>
       </c>
       <c r="C2079" t="n">
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.899233054837445</v>
+        <v>-5.855167298705535</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.675322917286278</v>
+        <v>1.692949219739042</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5017111854802323</v>
+        <v>0.5242565266745941</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.336399274823144</v>
+        <v>4.349926479539761</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884084</v>
+        <v>3.770053391710332</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.029604549479358</v>
+        <v>4.035372563535004</v>
       </c>
       <c r="D2080" t="n">
-        <v>-6.04283421886083</v>
+        <v>-5.855167298705535</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.612114437621278</v>
+        <v>1.692949219739042</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5017111854802323</v>
+        <v>0.5242565266745941</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.330631260767498</v>
+        <v>4.349926479539761</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129648</v>
+        <v>3.657773650705921</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.029604549479358</v>
+        <v>4.035372563535004</v>
       </c>
       <c r="D2081" t="n">
-        <v>-6.041885795742791</v>
+        <v>-5.854218875587496</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.612493806868494</v>
+        <v>1.693328588986258</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5017111854802323</v>
+        <v>0.5242565266745941</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.330631260767498</v>
+        <v>4.349926479539761</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052351</v>
+        <v>3.890931774628624</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.04233215746045</v>
+        <v>4.048100171516096</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.142155613701812</v>
+        <v>-5.954488693546518</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.585113487665977</v>
+        <v>1.665948269783741</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5017111854802323</v>
+        <v>0.5242565266745941</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.34335886874859</v>
+        <v>4.362654087520853</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813495</v>
+        <v>3.726937566389768</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.044278155884838</v>
+        <v>4.050046169940484</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.136163366913</v>
+        <v>-5.948496446757706</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.58945638480589</v>
+        <v>1.670291166923654</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5017111854802323</v>
+        <v>0.5242565266745941</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.345304867172977</v>
+        <v>4.364600085945241</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537944</v>
+        <v>3.751808755114217</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.037932291902607</v>
+        <v>4.043700305958253</v>
       </c>
       <c r="D2084" t="n">
-        <v>-6.047605405782233</v>
+        <v>-5.859938485626938</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.618533705275965</v>
+        <v>1.69936848739373</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5017111854802323</v>
+        <v>0.5242565266745941</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.338959003190746</v>
+        <v>4.358254221963009</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771816</v>
+        <v>3.745167129348089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.037240969341602</v>
+        <v>4.043008983397248</v>
       </c>
       <c r="D2085" t="n">
-        <v>-6.029846328279159</v>
+        <v>-5.842179408123864</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.624946013716191</v>
+        <v>1.705780795833955</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5017111854802323</v>
+        <v>0.5242565266745941</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.338267680629742</v>
+        <v>4.357562899402005</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109721</v>
+        <v>3.788098555685995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.050023155250189</v>
+        <v>4.055791169305835</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.930216177230091</v>
+        <v>-5.742549257074796</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.677580260044405</v>
+        <v>1.758415042162169</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6013413365292998</v>
+        <v>0.6238866777236616</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.410827957167769</v>
+        <v>4.430123175940032</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843996</v>
+        <v>3.785223505420269</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.239177420748915</v>
+        <v>4.244945434804562</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.979615685919102</v>
+        <v>-5.791948765763808</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.846974722067527</v>
+        <v>1.927809504185291</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6116001699610445</v>
+        <v>0.6341455111554063</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.606137522725542</v>
+        <v>4.625432741497805</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.77218650835186</v>
+        <v>3.758944466928133</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.226366093851778</v>
+        <v>4.232134107907424</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.772931212276726</v>
+        <v>-5.585264292121431</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.916837184627339</v>
+        <v>1.997671966745103</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8182846436034201</v>
+        <v>0.8408299847977819</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.71733688001383</v>
+        <v>4.736632098786093</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.76339283855127</v>
+        <v>3.750150797127543</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.228367607505882</v>
+        <v>4.234135621561529</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.807088107274252</v>
+        <v>-5.619421187118958</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.905175940282434</v>
+        <v>1.986010722400198</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7347008740626076</v>
+        <v>0.7572462152569694</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.669188131943447</v>
+        <v>4.68848335071571</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041111</v>
+        <v>3.792348523617385</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.58186472149555</v>
+        <v>4.587632735551196</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.714498628212795</v>
+        <v>-5.526831708057501</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.295708845896684</v>
+        <v>2.376543628014448</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7347008740626076</v>
+        <v>0.7572462152569694</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.022685245933115</v>
+        <v>5.041980464705378</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497403</v>
+        <v>3.818922313073676</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.586427833062654</v>
+        <v>4.592195847118299</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.78765923198594</v>
+        <v>-5.599992311830646</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.27100771595453</v>
+        <v>2.351842498072293</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7066796740283645</v>
+        <v>0.7292250152227264</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.010435637479673</v>
+        <v>5.029730856251936</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492296</v>
+        <v>3.84506884906857</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.636257774386181</v>
+        <v>4.642025788441827</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.735442922189598</v>
+        <v>-5.547776002034304</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.341724181196594</v>
+        <v>2.422558963314357</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7066796740283645</v>
+        <v>0.7292250152227264</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.0602655788032</v>
+        <v>5.079560797575463</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436478</v>
+        <v>3.831693555012751</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.645071744596192</v>
+        <v>4.650839758651838</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.682935594679104</v>
+        <v>-5.49526867452381</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.371541082410803</v>
+        <v>2.452375864528566</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7591870015388594</v>
+        <v>0.7817323427332213</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.100583945519508</v>
+        <v>5.11987916429177</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039487</v>
+        <v>3.835134824615761</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.640709328635389</v>
+        <v>4.646477342691035</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.697690918879244</v>
+        <v>-5.51002399872395</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.361276536769944</v>
+        <v>2.442111318887707</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7591870015388594</v>
+        <v>0.7817323427332213</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.096221529558705</v>
+        <v>5.115516748330967</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524482</v>
+        <v>3.854911074100755</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.631633832051669</v>
+        <v>4.637401846107315</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.648226295509333</v>
+        <v>-5.460559375354038</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.371986889534188</v>
+        <v>2.452821671651951</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8086516249087711</v>
+        <v>0.831196966103133</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.116824806996932</v>
+        <v>5.136120025769195</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867955</v>
+        <v>3.694312199127948</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.628041499766604</v>
+        <v>4.633809513822249</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.485118303355717</v>
+        <v>-5.303447198131892</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.433637754110569</v>
+        <v>2.512074210255745</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9717596170623863</v>
+        <v>0.98830914332528</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.211097270004036</v>
+        <v>5.226794999817417</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232971</v>
+        <v>3.887600205048849</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.637088536457732</v>
+        <v>4.633809513822249</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.46447521255449</v>
+        <v>-5.306197314121219</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.450942027122188</v>
+        <v>2.510974163860014</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9717596170623863</v>
+        <v>0.98830914332528</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.220144306695164</v>
+        <v>5.226794999817417</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179674</v>
+        <v>3.872929713995553</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.637946001443853</v>
+        <v>4.634666978808371</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.527183129029048</v>
+        <v>-5.368905230595777</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.426716325518486</v>
+        <v>2.486748462256312</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9090517005878286</v>
+        <v>0.9256012268507222</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.18337702179655</v>
+        <v>5.190027714918804</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967721</v>
+        <v>3.9020831257836</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.600855418234206</v>
+        <v>4.597576395598723</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.479175005185355</v>
+        <v>-5.320897106752084</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.408828991846315</v>
+        <v>2.468861128584141</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9090517005878286</v>
+        <v>0.9256012268507222</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.146286438586903</v>
+        <v>5.152937131709156</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018612</v>
+        <v>3.912757633834491</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.604787671792156</v>
+        <v>4.601508649156672</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.400349348001765</v>
+        <v>-5.242071449568494</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.444291508277702</v>
+        <v>2.504323645015527</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.9878773577714191</v>
+        <v>1.004426884034313</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.197514086455008</v>
+        <v>5.20416477957726</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075135</v>
+        <v>3.909006257891014</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.599686764399193</v>
+        <v>4.596407741763709</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.208414546747891</v>
+        <v>-5.05013664831462</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.515964521386289</v>
+        <v>2.575996658124113</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.9878773577714191</v>
+        <v>1.004426884034313</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.192413179062044</v>
+        <v>5.199063872184297</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435445</v>
+        <v>3.889827770251324</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.595040673788288</v>
+        <v>4.591761651152805</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.090241168729964</v>
+        <v>-4.931963270296693</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.558587781982555</v>
+        <v>2.61861991872038</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.106050735789346</v>
+        <v>1.12260026205224</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.258671115261897</v>
+        <v>5.265321808384149</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917734</v>
+        <v>3.876967000733613</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.624129266651315</v>
+        <v>4.620850244015831</v>
       </c>
       <c r="D2103" t="n">
-        <v>-5.001394051870466</v>
+        <v>-4.843116153437196</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.623215221589381</v>
+        <v>2.683247358327205</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.194897852648844</v>
+        <v>1.211447378911738</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.341067978240622</v>
+        <v>5.347718671362874</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.82800627401364</v>
+        <v>3.802434493323078</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.617689489662492</v>
+        <v>4.614410467027009</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.974345014177213</v>
+        <v>-4.803234567433103</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.627595059677859</v>
+        <v>2.692760215740019</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.221946890342098</v>
+        <v>1.25132896491583</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.350857623867752</v>
+        <v>5.365207845976507</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.82398744526377</v>
+        <v>3.844656489456963</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.617689489662492</v>
+        <v>4.614410467027009</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.980378294363983</v>
+        <v>-4.809267847619873</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.625181747603151</v>
+        <v>2.690346903665311</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.221946890342098</v>
+        <v>1.25132896491583</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.350857623867752</v>
+        <v>5.365207845976507</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170844</v>
+        <v>3.836326247364036</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.621327656804905</v>
+        <v>4.618048634169421</v>
       </c>
       <c r="D2106" t="n">
-        <v>-5.032230069937144</v>
+        <v>-4.861119623193034</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.608079204516299</v>
+        <v>2.673244360578459</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.170095114768936</v>
+        <v>1.199477189342669</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.323384725666267</v>
+        <v>5.337734947775022</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,45 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431406</v>
+        <v>3.852568539043109</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.584819403988742</v>
+        <v>4.581540381353258</v>
       </c>
       <c r="D2107" t="n">
-        <v>-5.059287516068971</v>
+        <v>-4.888177069324861</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.560747973247405</v>
+        <v>2.625913129309565</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.170095114768936</v>
+        <v>1.199477189342669</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.286876472850103</v>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" s="2" t="n">
-        <v>45570</v>
-      </c>
-      <c r="B2108" t="n">
-        <v>3.702899209171088</v>
-      </c>
-      <c r="C2108" t="n">
-        <v>4.511075558311259</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>-5.059287516068971</v>
-      </c>
-      <c r="E2108" t="n">
-        <v>2.560747973247405</v>
-      </c>
-      <c r="F2108" t="n">
-        <v>1.170095114768936</v>
-      </c>
-      <c r="G2108" t="n">
-        <v>4.504139355297627</v>
+        <v>5.301226694958859</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241005.xlsx
+++ b/tame_output/ON/bt/strategyON_20241005.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.8%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>146.5%</t>
+          <t>134.2%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>122.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-607.5%</t>
+          <t>-598.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.3%</t>
+          <t>424.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-650.4%</t>
+          <t>-657.9%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-243.4%</t>
+          <t>-239.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-113.6%</t>
+          <t>-129.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.5%</t>
+          <t>-204.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-104.0%</t>
+          <t>-106.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>102.0%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2107"/>
+  <dimension ref="A1:G2108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6545912063460799</v>
+        <v>-0.5680779336161021</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.859135855474547</v>
+        <v>2.893741164566538</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6432019696912785</v>
+        <v>-0.5566886969613007</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.861516346255708</v>
+        <v>2.896121655347699</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.8956798641106845</v>
+        <v>-0.8091665913807067</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.758452079993008</v>
+        <v>2.793057389084999</v>
       </c>
       <c r="F1847" t="n">
         <v>1.291969947040633</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.185811530716116</v>
+        <v>-1.099298257986138</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.642265629949757</v>
+        <v>2.676870939041748</v>
       </c>
       <c r="F1848" t="n">
         <v>1.316051741780813</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.393815589069193</v>
+        <v>-1.307302316339215</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.563956151162452</v>
+        <v>2.598561460254443</v>
       </c>
       <c r="F1849" t="n">
         <v>1.316051741780813</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.455994000230163</v>
+        <v>-1.369480727500185</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.534166243036052</v>
+        <v>2.568771552128043</v>
       </c>
       <c r="F1850" t="n">
         <v>1.253873330619843</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.822062727374816</v>
+        <v>-1.735549454644838</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.38082305148464</v>
+        <v>2.415428360576631</v>
       </c>
       <c r="F1851" t="n">
         <v>0.88780460347519</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.0305535088265</v>
+        <v>-1.944040236096523</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.317765028642734</v>
+        <v>2.352370337734726</v>
       </c>
       <c r="F1852" t="n">
         <v>0.6793138220235055</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.277754693591722</v>
+        <v>-2.191241420861744</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.226983305145214</v>
+        <v>2.261588614237206</v>
       </c>
       <c r="F1853" t="n">
         <v>0.699467175522318</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.770139721615819</v>
+        <v>-2.683626448885841</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.031135685979308</v>
+        <v>2.065740995071299</v>
       </c>
       <c r="F1854" t="n">
         <v>0.2070821474982212</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.02844348929949</v>
+        <v>-2.941930216569512</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.926356717718702</v>
+        <v>1.960962026810694</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.278314169314071</v>
+        <v>-3.191800896584093</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.828177569167486</v>
+        <v>1.862782878259478</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.484825946201093</v>
+        <v>-3.398312673471115</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.741678917068935</v>
+        <v>1.776284226160927</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.804170021281594</v>
+        <v>-3.717656748551617</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.615714213736994</v>
+        <v>1.650319522828986</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.190379852557369</v>
+        <v>-4.103866579827391</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.447563168694089</v>
+        <v>1.48216847778608</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.458931643255243</v>
+        <v>-4.372418370525265</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.32842722741703</v>
+        <v>1.363032536509021</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.1179447876207835</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.794594290485695</v>
+        <v>-4.708081017755718</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.192742760180814</v>
+        <v>1.227348069272805</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.1858757731096883</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.871038620688567</v>
+        <v>-4.784525347958589</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.168652588333907</v>
+        <v>1.203257897425898</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.1054302640160264</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.236166003327313</v>
+        <v>-5.149652730597336</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.02185615028424</v>
+        <v>1.056461459376231</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.4017410483150389</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.644754780507992</v>
+        <v>-5.558241507778014</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.857182183426727</v>
+        <v>0.8917874925187186</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.8103298254957174</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.758515192530857</v>
+        <v>-5.672001919800879</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.806863451089042</v>
+        <v>0.8414687601810336</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.8103298254957174</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.174907066817855</v>
+        <v>-6.088393794087876</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6383007519831203</v>
+        <v>0.6729060610751119</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.8103298254957174</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.536080696634842</v>
+        <v>-6.449567423904864</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5040899907250038</v>
+        <v>0.5386952998169958</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.8103298254957174</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.879339216277861</v>
+        <v>-6.792825943547883</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3628861480134917</v>
+        <v>0.3974914571054833</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.927542033520205</v>
+        <v>-6.841028760790227</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3420099411715549</v>
+        <v>0.3766152502635465</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.094350693494567</v>
+        <v>-7.007837420764589</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2790654531110186</v>
+        <v>0.3136707622030102</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.852613149208854</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.28107040180387</v>
+        <v>-7.194557129073892</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2003512652528943</v>
+        <v>0.2349565743448858</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.852613149208854</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.664071790546501</v>
+        <v>-7.577558517816523</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.04704860843425784</v>
+        <v>0.0816539175262494</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.852613149208854</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.66855823574789</v>
+        <v>-7.582044963017911</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.04782554632513225</v>
+        <v>0.08243085541712381</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8570995944102426</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.028088558251891</v>
+        <v>-7.941575285521913</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.09063627937841856</v>
+        <v>-0.05603097028642656</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8570995944102426</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.078437621706113</v>
+        <v>-7.991924348976135</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1028598848029296</v>
+        <v>-0.06825457571093763</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9074486578644647</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.089543626397532</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.1042605360577276</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.005067935285861</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.143615125905891</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.122995579539499</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.059139434794221</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.147190911997638</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.1189126968575556</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.084668356710713</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.180843750506112</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.1278912777765089</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.185081724627751</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.319929865124969</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.168154022130631</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.324167839246607</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.495054282511513</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.2236485683377314</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.499292256633151</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.729506376526002</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.3246485708451234</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.499292256633151</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-8.833881107552449</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.3730706540296782</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.603666987659597</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-8.996394573251033</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.4369602504705554</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.701300418078284</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.122431366619322</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.4846812391887565</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.676048795268541</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-9.065359594723391</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.4578621947439832</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.676048795268541</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.207031436447512</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.516006158332373</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.676048795268541</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.157440592022677</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.4811164103975671</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.626457950843708</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-9.008522257550821</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.4346002102555073</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.595208360108535</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.782677104831411</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.3346830761315349</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.553281684521371</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.658098448493819</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.2837124690404393</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.553281684521371</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.633061766925309</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.2710640222509273</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.527952596970635</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.560928591637428</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.2364770478971385</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.527952596970635</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.644238203941597</v>
+        <v>-8.557724931211622</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2795381552126726</v>
+        <v>-0.2449328461206814</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.524748936544829</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.550779169956373</v>
+        <v>-8.464265897226397</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2520380229314902</v>
+        <v>-0.2174327138394991</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.524748936544829</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.540125988402941</v>
+        <v>-8.453612715672966</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2496113108094913</v>
+        <v>-0.2150060017175002</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.524748936544829</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.442218949726451</v>
+        <v>-8.355705676996475</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.210748810312356</v>
+        <v>-0.1761435012203649</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.456763186684273</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.418265408750493</v>
+        <v>-8.331752136020517</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2004988877764791</v>
+        <v>-0.165893578684488</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.432809645708315</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.154205470427696</v>
+        <v>-8.067692197697721</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1081352286091124</v>
+        <v>-0.07352991951712173</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.168749707385519</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.447125846922858</v>
+        <v>-7.360612574192882</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.171909587132522</v>
+        <v>0.2065148962245127</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.168749707385519</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.406941548556667</v>
+        <v>-7.320428275826692</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1883269303668396</v>
+        <v>0.2229322394588302</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.128565409019328</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.243541677617305</v>
+        <v>-7.157028404887329</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2530536999633415</v>
+        <v>0.2876590090553321</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9651655380799653</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.08542429823853</v>
+        <v>-6.998911025508554</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3242250805527038</v>
+        <v>0.3588303896446949</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8070481587011898</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.935757907231014</v>
+        <v>-6.849244634501039</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.381199426642751</v>
+        <v>0.4158047357347416</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7141446674586539</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.803482433600128</v>
+        <v>-6.716969160870152</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3353704021022601</v>
+        <v>0.3699757111942508</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.5818691938277673</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.631621218035225</v>
+        <v>-6.54510794530525</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4069299490158578</v>
+        <v>0.4415352581078489</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4100079782628644</v>
@@ -45412,10 +45412,10 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.546656551305906</v>
+        <v>-6.460143278575931</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4538221569312442</v>
+        <v>0.4884274660232353</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.3250433115335448</v>
@@ -45435,10 +45435,10 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.652246541079011</v>
+        <v>-6.565733268349035</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2836102314227835</v>
+        <v>0.3182155405147746</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.4306333013066492</v>
@@ -45458,10 +45458,10 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.584011956453583</v>
+        <v>-6.497498683723608</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3594484071500412</v>
+        <v>0.3940537162420319</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.4122179784341132</v>
@@ -45481,10 +45481,10 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.436071915045984</v>
+        <v>-6.349558642316008</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3020036150746739</v>
+        <v>0.3366089241666645</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3918970625255556</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.383102392791995</v>
+        <v>-6.29658912006202</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.314477437722791</v>
+        <v>0.3490827468147817</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.3389275402715667</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.217314196831705</v>
+        <v>-6.130800924101729</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.373832104011814</v>
+        <v>0.4084374131038051</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.3389275402715667</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.183950990352936</v>
+        <v>-6.09743771762296</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4016397409844648</v>
+        <v>0.4362450500764554</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.3389275402715667</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.075691853230414</v>
+        <v>-5.989178580500439</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4394755162926685</v>
+        <v>0.4740808253846596</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.3389275402715667</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.952400718413283</v>
+        <v>-5.865887445683308</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4862900642300976</v>
+        <v>0.5208953733220887</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.2156364054544362</v>
@@ -45619,10 +45619,10 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.899703851281992</v>
+        <v>-5.813190578552017</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5150697893199392</v>
+        <v>0.5496750984119303</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1629395383231451</v>
@@ -45642,10 +45642,10 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.655938409298548</v>
+        <v>-5.569425136568572</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6083566744603677</v>
+        <v>0.6429619835523588</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1629395383231451</v>
@@ -45665,10 +45665,10 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.566162736922076</v>
+        <v>-5.4796494641921</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6463912573309725</v>
+        <v>0.6809965664229636</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.101340093408835</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.316312342973001</v>
+        <v>-5.229799070243025</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7390734898943045</v>
+        <v>0.7736787989862957</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.101340093408835</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.140420250505569</v>
+        <v>-5.053906977775593</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8130294504019262</v>
+        <v>0.8476347594939173</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.101340093408835</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.968973787483105</v>
+        <v>-4.88246051475313</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8949355416654652</v>
+        <v>0.9295408507574563</v>
       </c>
       <c r="F1921" t="n">
         <v>0.07010636961362809</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.888951500373985</v>
+        <v>-4.802438227644009</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9259649341254106</v>
+        <v>0.9605702432174015</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1501286567227491</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.82531575814005</v>
+        <v>-4.738802485410075</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9561140320733017</v>
+        <v>0.9907193411652926</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2137643989566836</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.731618439923655</v>
+        <v>-4.645105167193679</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9747872181436554</v>
+        <v>1.009392527235646</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2137643989566836</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.742121062988944</v>
+        <v>-4.655607790258968</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9723292455424173</v>
+        <v>1.006934554634408</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2032617758913947</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.629634802320069</v>
+        <v>-4.543121529590094</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.021253063644787</v>
+        <v>1.055858372736778</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2032617758913947</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.611921115442204</v>
+        <v>-4.525407842712228</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.029017122313273</v>
+        <v>1.063622431405264</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2064431047883115</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.488446844129186</v>
+        <v>-4.40193357139921</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.075404902058474</v>
+        <v>1.110010211150465</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2064431047883115</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.43051101213097</v>
+        <v>-4.343997739400995</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.100158271868374</v>
+        <v>1.134763580960366</v>
       </c>
       <c r="F1929" t="n">
         <v>0.2320049794710608</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.297643323067692</v>
+        <v>-4.211130050337717</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.169199530295509</v>
+        <v>1.2038048393875</v>
       </c>
       <c r="F1930" t="n">
         <v>0.2320049794710608</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.177470239703194</v>
+        <v>-4.090956966973218</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.21841460808161</v>
+        <v>1.253019917173601</v>
       </c>
       <c r="F1931" t="n">
         <v>0.3521780628355597</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.042216878373217</v>
+        <v>-3.955703605643241</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.282604055175041</v>
+        <v>1.317209364267032</v>
       </c>
       <c r="F1932" t="n">
         <v>0.4874314241655369</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.102091705730909</v>
+        <v>-4.015578433000933</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24469161563339</v>
+        <v>1.279296924725381</v>
       </c>
       <c r="F1933" t="n">
         <v>0.4275565968078447</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.982271474820072</v>
+        <v>-3.895758202090096</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.307908877231933</v>
+        <v>1.342514186323924</v>
       </c>
       <c r="F1934" t="n">
         <v>0.4275565968078447</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.984741181281878</v>
+        <v>-3.898227908551902</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.214565193969652</v>
+        <v>1.249170503061643</v>
       </c>
       <c r="F1935" t="n">
         <v>0.4250868903460386</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.053111367605887</v>
+        <v>-3.966598094875912</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10647898092535</v>
+        <v>1.141084290017341</v>
       </c>
       <c r="F1936" t="n">
         <v>0.4343625893822535</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.164983647232038</v>
+        <v>-4.078470374502063</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.052166777706781</v>
+        <v>1.086772086798772</v>
       </c>
       <c r="F1937" t="n">
         <v>0.4343625893822535</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.14900898174577</v>
+        <v>-4.062495709015795</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.025131168825316</v>
+        <v>1.059736477917306</v>
       </c>
       <c r="F1938" t="n">
         <v>0.4343625893822535</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.153103528416768</v>
+        <v>-4.066590255686792</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.028060582148704</v>
+        <v>1.062665891240695</v>
       </c>
       <c r="F1939" t="n">
         <v>0.4343625893822535</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.145179153831854</v>
+        <v>-4.058665881101878</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.006972360743877</v>
+        <v>1.041577669835868</v>
       </c>
       <c r="F1940" t="n">
         <v>0.4343625893822535</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.138900951262005</v>
+        <v>-4.052387678532029</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9380219551732663</v>
+        <v>0.9726272642652574</v>
       </c>
       <c r="F1941" t="n">
         <v>0.4406407919521026</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.079048332058282</v>
+        <v>-3.992535059328306</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.972135389286888</v>
+        <v>1.006740698378879</v>
       </c>
       <c r="F1942" t="n">
         <v>0.4406407919521026</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.992804869031904</v>
+        <v>-3.906291596301928</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.001579045071299</v>
+        <v>1.03618435416329</v>
       </c>
       <c r="F1943" t="n">
         <v>0.4406407919521026</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.038111688430884</v>
+        <v>-3.951598415700908</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.975232092756233</v>
+        <v>1.009837401848224</v>
       </c>
       <c r="F1944" t="n">
         <v>0.3998306289428718</v>
@@ -46286,10 +46286,10 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.067144793133185</v>
+        <v>-3.98063152040321</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9641707239084141</v>
+        <v>0.998776033000405</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3998306289428718</v>
@@ -46309,10 +46309,10 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.974334311682326</v>
+        <v>-3.88782103895235</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9305676083801235</v>
+        <v>0.9651729174721142</v>
       </c>
       <c r="F1946" t="n">
         <v>0.4926411103937312</v>
@@ -46332,10 +46332,10 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.018723781011754</v>
+        <v>-3.932210508281778</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9146852965729531</v>
+        <v>0.9492906056649439</v>
       </c>
       <c r="F1947" t="n">
         <v>0.4482516410643035</v>
@@ -46355,10 +46355,10 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.998220087126256</v>
+        <v>-3.911706814396281</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.917962482638875</v>
+        <v>0.9525677917308659</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4687553349498008</v>
@@ -46378,10 +46378,10 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.081892183838589</v>
+        <v>-3.995378911108613</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8899849397846094</v>
+        <v>0.9245902488766005</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4687553349498008</v>
@@ -46401,10 +46401,10 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.109672581739941</v>
+        <v>-4.023159309009966</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8903699823926072</v>
+        <v>0.9249752914845981</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4409749370484478</v>
@@ -46424,10 +46424,10 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.22805325447008</v>
+        <v>-4.141539981740104</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6813734333012051</v>
+        <v>0.715978742393196</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3737570848974716</v>
@@ -46447,10 +46447,10 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.336667332913411</v>
+        <v>-4.250154060183435</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7580774626430784</v>
+        <v>0.7926827717350693</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3737570848974716</v>
@@ -46470,10 +46470,10 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.301258294665268</v>
+        <v>-4.214745021935292</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7867541040446584</v>
+        <v>0.8213594131366495</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3737570848974716</v>
@@ -46493,10 +46493,10 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.309719463320729</v>
+        <v>-4.223206190590753</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.780789077924843</v>
+        <v>0.8153943870168339</v>
       </c>
       <c r="F1954" t="n">
         <v>0.3652959162420105</v>
@@ -46516,10 +46516,10 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.132603133285563</v>
+        <v>-4.046089860555587</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8483646387842116</v>
+        <v>0.8829699478762025</v>
       </c>
       <c r="F1955" t="n">
         <v>0.3652959162420105</v>
@@ -46539,10 +46539,10 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.177695378119108</v>
+        <v>-4.091182105389133</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8310111326127065</v>
+        <v>0.8656164417046974</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3033998730726207</v>
@@ -46562,10 +46562,10 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.998319956880341</v>
+        <v>-3.911806684150365</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.896548276414628</v>
+        <v>0.9311535855066189</v>
       </c>
       <c r="F1957" t="n">
         <v>0.4601766312433394</v>
@@ -46585,10 +46585,10 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.043334170400946</v>
+        <v>-3.956820897670971</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8593500463379753</v>
+        <v>0.8939553554299662</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4298277359287348</v>
@@ -46608,10 +46608,10 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.131345356959644</v>
+        <v>-4.044832084229668</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8298371340534423</v>
+        <v>0.8644424431454332</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3643512280695618</v>
@@ -46631,10 +46631,10 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.232543138396816</v>
+        <v>-4.146029865666841</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7885619433750746</v>
+        <v>0.8231672524670655</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2959424145242426</v>
@@ -46654,10 +46654,10 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.226032171782504</v>
+        <v>-4.139518899052528</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7887662915751164</v>
+        <v>0.8233716006671072</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2959424145242426</v>
@@ -46677,10 +46677,10 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.206994044075206</v>
+        <v>-4.120480771345231</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7929062618662801</v>
+        <v>0.8275115709582712</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2377588031930481</v>
@@ -46700,10 +46700,10 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.259509846350027</v>
+        <v>-4.172996573620051</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8911943425905424</v>
+        <v>0.9257996516825333</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2377588031930481</v>
@@ -46723,10 +46723,10 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.262918157784607</v>
+        <v>-4.176404885054631</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8906643470028439</v>
+        <v>0.925269656094835</v>
       </c>
       <c r="F1964" t="n">
         <v>0.2702753722024255</v>
@@ -46746,10 +46746,10 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.243562021890759</v>
+        <v>-4.157048749160784</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9044153317573089</v>
+        <v>0.9390206408492998</v>
       </c>
       <c r="F1965" t="n">
         <v>0.2702753722024255</v>
@@ -46769,10 +46769,10 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.316891550628852</v>
+        <v>-4.230378277898876</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7730337415392714</v>
+        <v>0.8076390506312623</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2706700346220474</v>
@@ -46792,10 +46792,10 @@
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.40071277190355</v>
+        <v>-4.314199499173575</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6492289702730232</v>
+        <v>0.6838342793650141</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2706700346220474</v>
@@ -46815,10 +46815,10 @@
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.394560065850766</v>
+        <v>-4.30804679312079</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6523524010857953</v>
+        <v>0.6869577101777862</v>
       </c>
       <c r="F1968" t="n">
         <v>0.2768227406748317</v>
@@ -46838,10 +46838,10 @@
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.411369364001268</v>
+        <v>-4.324856091271292</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6447091585657048</v>
+        <v>0.6793144676576957</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2600134425243301</v>
@@ -46861,10 +46861,10 @@
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.349071365225146</v>
+        <v>-4.26255809249517</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7359639118729746</v>
+        <v>0.7705692209649655</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3053077067987721</v>
@@ -46884,10 +46884,10 @@
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.147281167559988</v>
+        <v>-4.060767894830012</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6189719926531647</v>
+        <v>0.6535773017451558</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5033258989679266</v>
@@ -46907,10 +46907,10 @@
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.198167880246182</v>
+        <v>-4.111654607516207</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6689075399008622</v>
+        <v>0.703512848992853</v>
       </c>
       <c r="F1972" t="n">
         <v>0.452439186281732</v>
@@ -46930,10 +46930,10 @@
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.111557137596376</v>
+        <v>-4.0250438648664</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7181795730768286</v>
+        <v>0.7527848821688194</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5310649174868902</v>
@@ -46953,10 +46953,10 @@
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.17176643560166</v>
+        <v>-4.085253162871685</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6926318346993863</v>
+        <v>0.7272371437913772</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4708556194816057</v>
@@ -46976,10 +46976,10 @@
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.122579786917309</v>
+        <v>-4.036066514187334</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7107981122130553</v>
+        <v>0.7454034213050462</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46999,10 +46999,10 @@
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.07820665527874</v>
+        <v>-3.991693382548765</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.728410232303919</v>
+        <v>0.7630155413959099</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47022,10 +47022,10 @@
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.04347533396024</v>
+        <v>-3.956962061230264</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7366965549699098</v>
+        <v>0.7713018640619009</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.995819603399184</v>
+        <v>-3.909306330669208</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7621406042221368</v>
+        <v>0.7967459133141277</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.895301444900429</v>
+        <v>-3.808788172170454</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8072402409963635</v>
+        <v>0.8418455500883544</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.879396115468077</v>
+        <v>-3.792882842738101</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8003570452451767</v>
+        <v>0.8349623543371676</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.834557713859679</v>
+        <v>-3.748044441129703</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8223901084991645</v>
+        <v>0.8569954175911554</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.854056170101687</v>
+        <v>-3.767542897371711</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8187516656334393</v>
+        <v>0.8533569747254302</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.82668474540596</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.809853333015786</v>
+        <v>-3.723340060285811</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8423124029956366</v>
+        <v>0.8769177120876275</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.817412998852833</v>
+        <v>-3.730899726122858</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8376985371300654</v>
+        <v>0.8723038462220563</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.659121581313561</v>
+        <v>-3.572608308583586</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9522628693288138</v>
+        <v>0.9868681784208047</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.451479577679085</v>
+        <v>-3.364966304949109</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.033760375376857</v>
+        <v>1.068365684468848</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.400447484956557</v>
+        <v>-3.313934212226581</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.049121440704139</v>
+        <v>1.08372674979613</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.335223303829351</v>
+        <v>-3.248710031099376</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.092398517247726</v>
+        <v>1.127003826339717</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.297796283758217</v>
+        <v>-3.211283011028242</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.10333029757546</v>
+        <v>1.137935606667451</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.296438298784672</v>
+        <v>-3.209925026054696</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.105130283896118</v>
+        <v>1.139735592988109</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.268025035684788</v>
+        <v>-3.181511762954813</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.277053360157282</v>
+        <v>1.311658669249273</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.193242774659776</v>
+        <v>-3.1067295019298</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.427079173785105</v>
+        <v>1.461684482877096</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.167158690395968</v>
+        <v>-3.080645417665992</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.429220783504487</v>
+        <v>1.463826092596478</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.079280777286847</v>
+        <v>-2.992767504556872</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.462565144331915</v>
+        <v>1.497170453423906</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.070388315893564</v>
+        <v>-2.983875043163589</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.483676534616019</v>
+        <v>1.51828184370801</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.238864432863442</v>
+        <v>-3.152351160133466</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.408141135232652</v>
+        <v>1.442746444324643</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.792608240234002</v>
+        <v>-2.706094967504026</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.56791330947229</v>
+        <v>1.602518618564281</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47505,10 +47505,10 @@
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.76988713655085</v>
+        <v>-2.683373863820874</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.567665773442456</v>
+        <v>1.602271082534446</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47528,10 +47528,10 @@
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.899088949844892</v>
+        <v>-2.812575677114916</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.674891173976008</v>
+        <v>1.709496483067998</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47551,10 +47551,10 @@
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.924963348318918</v>
+        <v>-2.838450075588942</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.701619237080044</v>
+        <v>1.736224546172035</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47574,10 +47574,10 @@
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.917908658103744</v>
+        <v>-2.831395385373769</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.701116469155658</v>
+        <v>1.735721778247649</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
@@ -47597,10 +47597,10 @@
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.890957433777256</v>
+        <v>-2.804444161047281</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.721903112530995</v>
+        <v>1.756508421622986</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
@@ -47620,10 +47620,10 @@
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.912501661608043</v>
+        <v>-2.825988388878068</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.89738855354364</v>
+        <v>1.931993862635631</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
@@ -47643,10 +47643,10 @@
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.934909779412915</v>
+        <v>-2.84839650668294</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.880542001324684</v>
+        <v>1.915147310416675</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
@@ -47666,10 +47666,10 @@
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.963134014990516</v>
+        <v>-2.87662074226054</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.871306306643282</v>
+        <v>1.905911615735272</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
@@ -47689,10 +47689,10 @@
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.972574940879046</v>
+        <v>-2.88606166814907</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.923783654009717</v>
+        <v>1.958388963101708</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
@@ -47712,10 +47712,10 @@
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.178813878667479</v>
+        <v>-3.092300605937504</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.844179173439644</v>
+        <v>1.878784482531635</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9241185524652205</v>
@@ -47735,10 +47735,10 @@
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.255143856268385</v>
+        <v>-3.168630583538409</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.811758995293057</v>
+        <v>1.846364304385048</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9241185524652205</v>
@@ -47758,10 +47758,10 @@
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.410100641668514</v>
+        <v>-3.323587368938539</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.744596510735868</v>
+        <v>1.779201819827859</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7691617670650912</v>
@@ -47781,10 +47781,10 @@
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.571669067195769</v>
+        <v>-3.485155794465794</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.678403150735118</v>
+        <v>1.713008459827109</v>
       </c>
       <c r="F2010" t="n">
         <v>0.6423788432672118</v>
@@ -47804,10 +47804,10 @@
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.679969729065889</v>
+        <v>-3.593456456335913</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.648156292852989</v>
+        <v>1.68276160194498</v>
       </c>
       <c r="F2011" t="n">
         <v>0.6423788432672118</v>
@@ -47827,10 +47827,10 @@
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.839520801829406</v>
+        <v>-3.75300752909943</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.576341060530522</v>
+        <v>1.610946369622513</v>
       </c>
       <c r="F2012" t="n">
         <v>0.4901011764054604</v>
@@ -47850,10 +47850,10 @@
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.867421588938879</v>
+        <v>-3.780908316208903</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.563704786813735</v>
+        <v>1.598310095905726</v>
       </c>
       <c r="F2013" t="n">
         <v>0.4555042522625256</v>
@@ -47873,10 +47873,10 @@
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.989947691641773</v>
+        <v>-3.903434418911797</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.511458789709776</v>
+        <v>1.546064098801767</v>
       </c>
       <c r="F2014" t="n">
         <v>0.3329781495596317</v>
@@ -47896,10 +47896,10 @@
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.220462187827361</v>
+        <v>-4.133948915097386</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.485958950826044</v>
+        <v>1.520564259918035</v>
       </c>
       <c r="F2015" t="n">
         <v>0.102463653374043</v>
@@ -47919,10 +47919,10 @@
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.569207273051805</v>
+        <v>-4.482694000321829</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.486772635738114</v>
+        <v>1.521377944830105</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.006284300544854848</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.723193690827945</v>
+        <v>-4.63668041809797</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.494158337773297</v>
+        <v>1.528763646865288</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.006284300544854848</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.927793125690954</v>
+        <v>-4.841279852960978</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.398369765948215</v>
+        <v>1.432975075040206</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.006284300544854848</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.180268279698678</v>
+        <v>-5.093755006968703</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.309250193400539</v>
+        <v>1.34385550249253</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.006284300544854848</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.47316403617809</v>
+        <v>-5.386650763448115</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.193302425327718</v>
+        <v>1.227907734419709</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.006284300544854848</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.659828164312898</v>
+        <v>-5.573314891582923</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.122758516301116</v>
+        <v>1.157363825393107</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.03302327136941474</v>
@@ -48057,10 +48057,10 @@
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.805848851226861</v>
+        <v>-5.719335578496885</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.059428094271721</v>
+        <v>1.094033403363712</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.04210636316327171</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.897562860336446</v>
+        <v>-5.811049587606471</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.18494654732693</v>
+        <v>1.219551856418922</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.04210636316327171</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.929214519396416</v>
+        <v>-5.84270124666644</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.167132521666757</v>
+        <v>1.201737830758748</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.04727482040771191</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.75004401586815</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.998280573969352</v>
+        <v>-5.911767301239377</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.149735517406073</v>
+        <v>1.184340826498064</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.1096456979013219</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332697</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.10025669621776</v>
+        <v>-6.013743423487784</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.117870706962613</v>
+        <v>1.152476016054604</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.2116218201497295</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231814</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.990250412740538</v>
+        <v>-5.903737140010563</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.154026107597677</v>
+        <v>1.188631416689668</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.1884172482324543</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.002780117852417</v>
+        <v>-5.916266845122442</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.1532642362749</v>
+        <v>1.18786954536689</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.2022437476989773</v>
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.56199359061215</v>
+        <v>3.433772579176956</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.70133339238058</v>
+        <v>-5.614820119650604</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.281103809346171</v>
+        <v>1.187488107002967</v>
       </c>
       <c r="F2029" t="n">
         <v>0.09920297777285991</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.621515377275867</v>
+        <v>3.493294365840672</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.562964768364861</v>
+        <v>3.434743756929666</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.725923636615764</v>
+        <v>-5.639410363885788</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.272238889404808</v>
+        <v>1.178623187061604</v>
       </c>
       <c r="F2030" t="n">
         <v>0.09920297777285991</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.622486555028577</v>
+        <v>3.494265543593382</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.563807672744617</v>
+        <v>3.435586661309422</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.674885260609243</v>
+        <v>-5.588371987879268</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.293497144187171</v>
+        <v>1.199881441843967</v>
       </c>
       <c r="F2031" t="n">
         <v>0.09920297777285991</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.623329459408333</v>
+        <v>3.495108447973138</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.582845771618762</v>
+        <v>3.454624760183567</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.646036583785783</v>
+        <v>-5.559523311055807</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.324074713790701</v>
+        <v>1.230459011447497</v>
       </c>
       <c r="F2032" t="n">
         <v>0.1280516545963202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.659676764376554</v>
+        <v>3.531455752941359</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.399029767742697</v>
+        <v>3.270808756307502</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.549401671767143</v>
+        <v>-5.462888399037167</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.178912674722091</v>
+        <v>1.085296972378888</v>
       </c>
       <c r="F2033" t="n">
         <v>0.2246865666149601</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.533841707711673</v>
+        <v>3.405620696276478</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077642</v>
+        <v>3.804688961077644</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.402531811816661</v>
+        <v>3.274310800381466</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.480363660818675</v>
+        <v>-5.393850388088699</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.210029923175443</v>
+        <v>1.116414220832239</v>
       </c>
       <c r="F2034" t="n">
         <v>0.2937245775634282</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.578766558354718</v>
+        <v>3.450545546919523</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.775028860833464</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.386958630892743</v>
+        <v>3.258737619457548</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.461576560449736</v>
+        <v>-5.375063287719761</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.201971582399101</v>
+        <v>1.108355880055897</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3125116779323667</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.574465637652164</v>
+        <v>3.446244626216969</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.386146341329173</v>
+        <v>3.257925329893978</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.384477958907864</v>
+        <v>-5.297964686177888</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.23199873345228</v>
+        <v>1.138383031109075</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3125116779323667</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.573653348088593</v>
+        <v>3.445432336653398</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.396015120454245</v>
+        <v>3.267794109019051</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.394863153797753</v>
+        <v>-5.308349881067778</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.237713434621396</v>
+        <v>1.144097732278192</v>
       </c>
       <c r="F2037" t="n">
         <v>0.3021264830424774</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.577291010279732</v>
+        <v>3.449069998844537</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735286</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.466852126230671</v>
+        <v>3.338631114795476</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.413451312519978</v>
+        <v>-5.326938039790003</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.301115176908931</v>
+        <v>1.207499474565727</v>
       </c>
       <c r="F2038" t="n">
         <v>0.283538324320252</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.636975120822822</v>
+        <v>3.508754109387627</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.463721137048969</v>
+        <v>3.335500125613774</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.413749859216014</v>
+        <v>-5.327236586486038</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.297864769048815</v>
+        <v>1.204249066705612</v>
       </c>
       <c r="F2039" t="n">
         <v>0.2832397776242161</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.633665003623499</v>
+        <v>3.505443992188304</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108862</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.468252031988361</v>
+        <v>3.340031020553166</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.312926725525586</v>
+        <v>-5.226413452795611</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.342724917464378</v>
+        <v>1.249109215121174</v>
       </c>
       <c r="F2040" t="n">
         <v>0.2957039931085699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.645674427853503</v>
+        <v>3.517453416418308</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121472</v>
+        <v>3.807356168121474</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.468381285466904</v>
+        <v>3.340160274031709</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.122145364773178</v>
+        <v>-5.035632092043203</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.419166715243884</v>
+        <v>1.32555101290068</v>
       </c>
       <c r="F2041" t="n">
         <v>0.4864853538609773</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.76027249778349</v>
+        <v>3.632051486348296</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906085</v>
+        <v>3.775233033906087</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.4482181312045</v>
+        <v>3.319997119769305</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.015182006923757</v>
+        <v>-4.928668734193781</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.44178890412125</v>
+        <v>1.348173201778046</v>
       </c>
       <c r="F2042" t="n">
         <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.775188108296968</v>
+        <v>3.646967096861773</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912991</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.483185067816559</v>
+        <v>3.354964056381364</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.959851419021994</v>
+        <v>-4.873338146292019</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.498888075894013</v>
+        <v>1.405272373550809</v>
       </c>
       <c r="F2043" t="n">
         <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.843353397650084</v>
+        <v>3.715132386214889</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539899</v>
+        <v>3.743767956539901</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.476871635717997</v>
+        <v>3.348650624282802</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.947797292109032</v>
+        <v>-4.861284019379056</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.497396294560636</v>
+        <v>1.403780592217432</v>
       </c>
       <c r="F2044" t="n">
         <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.844272441699299</v>
+        <v>3.716051430264104</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811014</v>
+        <v>3.725010844811016</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.478752265902132</v>
+        <v>3.350531254466937</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.025152782237001</v>
+        <v>-4.938639509507025</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.468334728693584</v>
+        <v>1.37471902635038</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.799739777806653</v>
+        <v>3.671518766371458</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382925</v>
+        <v>3.612322444382927</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.491603291780015</v>
+        <v>3.36338228034482</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.957104219545471</v>
+        <v>-4.870590946815495</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.508405179648078</v>
+        <v>1.414789477304875</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6030277491990641</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.853419941299454</v>
+        <v>3.725198929864259</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013432</v>
+        <v>3.645256780013434</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.511805961953609</v>
+        <v>3.383584950518414</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.188704612714972</v>
+        <v>-5.102191339984996</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.435967692553872</v>
+        <v>1.342351990210668</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6030277491990641</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.873622611473048</v>
+        <v>3.745401600037853</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.495412198020491</v>
+        <v>3.367191186585296</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.238756158244191</v>
+        <v>-5.152242885514216</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.399553310409066</v>
+        <v>1.305937608065863</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6030277491990641</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.85722884753993</v>
+        <v>3.729007836104735</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.455664111613958</v>
+        <v>3.327443100178763</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.413862990820636</v>
+        <v>-5.327349718090661</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.289762490971955</v>
+        <v>1.196146788628751</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6030277491990641</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.817480761133397</v>
+        <v>3.689259749698202</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.462686730610898</v>
+        <v>3.334465719175703</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.217762837390113</v>
+        <v>-5.131249564660138</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.375225171341104</v>
+        <v>1.281609468997901</v>
       </c>
       <c r="F2050" t="n">
         <v>0.799127902629587</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.94216347218865</v>
+        <v>3.813942460753455</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395089</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.561857730183802</v>
+        <v>3.433636718748607</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.064737445276829</v>
+        <v>-4.978224172546853</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.535606327759323</v>
+        <v>1.441990625416119</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9521532947428711</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.133149707029525</v>
+        <v>4.00492869559433</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.749323955092095</v>
+        <v>3.6211029436569</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.093044759150099</v>
+        <v>-5.006531486420124</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.711749627118307</v>
+        <v>1.618133924775103</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9521532947428711</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.320615931937818</v>
+        <v>4.192394920502623</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620436</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.718726906446177</v>
+        <v>3.590505895010982</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.259637984263621</v>
+        <v>-5.173124711533646</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.614515288426981</v>
+        <v>1.520899586083777</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7855600696293488</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.190062948223787</v>
+        <v>4.061841936788592</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285649</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.722403309107895</v>
+        <v>3.5941822976727</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.236602190902055</v>
+        <v>-5.15008891817208</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.627406008433325</v>
+        <v>1.533790306090121</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7855600696293488</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.193739350885505</v>
+        <v>4.06551833945031</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.72002136423139</v>
+        <v>3.591800352796195</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.207356210446359</v>
+        <v>-5.120842937716383</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.636722455739099</v>
+        <v>1.543106753395895</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7855600696293488</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.191357406009</v>
+        <v>4.063136394573805</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.717314603389025</v>
+        <v>3.58909359195383</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.31428175832421</v>
+        <v>-5.227768485594234</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.591245475745593</v>
+        <v>1.49762977340239</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6786345217514974</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.124495316439925</v>
+        <v>3.99627430500473</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.71874340553226</v>
+        <v>3.590522394097065</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.459300316831459</v>
+        <v>-5.372787044101483</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.534666854485928</v>
+        <v>1.441051152142724</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5336159632442489</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.038912983478809</v>
+        <v>3.910691972043614</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.818674644790013</v>
+        <v>3.690453633354818</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.577642082616176</v>
+        <v>-5.491128809886201</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.587261387429794</v>
+        <v>1.49364568508659</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5443020018071389</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.145255845874297</v>
+        <v>4.017034834439102</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.714879051790808</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.816460341915952</v>
+        <v>3.688239330480757</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.629052504936884</v>
+        <v>-5.542539232206908</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.56448291562745</v>
+        <v>1.470867213284246</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5443020018071389</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.143041543000235</v>
+        <v>4.01482053156504</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.704757949437337</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.816363469990241</v>
+        <v>3.688142458555046</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.708471956144636</v>
+        <v>-5.62195868341466</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.532618263218639</v>
+        <v>1.439002560875434</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5443020018071389</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.142944671074525</v>
+        <v>4.01472365963933</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298403</v>
+        <v>3.736804952298405</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.816357363548284</v>
+        <v>3.688136352113089</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.803934954061853</v>
+        <v>-5.717421681331878</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.494426957609794</v>
+        <v>1.400811255266591</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5443020018071389</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.142938564632567</v>
+        <v>4.014717553197372</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218006</v>
+        <v>3.715372960218008</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.814453760110895</v>
+        <v>3.6862327486757</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.739559043211139</v>
+        <v>-5.653045770481163</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.518273718512691</v>
+        <v>1.424658016169487</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6086779126578541</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.179660507705607</v>
+        <v>4.051439496270413</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.736089413353543</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.820187577858621</v>
+        <v>3.691966566423426</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.794928205343332</v>
+        <v>-5.708414932613357</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.50185987140754</v>
+        <v>1.408244169064336</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6086779126578541</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.185394325453334</v>
+        <v>4.057173314018139</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113285</v>
+        <v>3.736822870113286</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.819725941201554</v>
+        <v>3.691504929766359</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.813146672340941</v>
+        <v>-5.726633399610965</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.494110847951429</v>
+        <v>1.400495145608225</v>
       </c>
       <c r="F2064" t="n">
         <v>0.5835714754020119</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.169868826442761</v>
+        <v>4.041647815007567</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113693</v>
+        <v>3.790272500113695</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.839600334051872</v>
+        <v>3.711379322616677</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.77446323699701</v>
+        <v>-5.687949964267035</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.52945861493932</v>
+        <v>1.435842912596116</v>
       </c>
       <c r="F2065" t="n">
         <v>0.5835714754020119</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.18974321929308</v>
+        <v>4.061522207857885</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.79448684401644</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.8233010345766</v>
+        <v>3.695080023141405</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.668428241791701</v>
+        <v>-5.581914969061725</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.555573313546172</v>
+        <v>1.461957611202968</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5835714754020119</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.173443919817807</v>
+        <v>4.045222908382613</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.825731984040646</v>
+        <v>3.697510972605451</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.485216578658606</v>
+        <v>-5.39870330592863</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.631288928263456</v>
+        <v>1.537673225920252</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5835714754020119</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.175874869281854</v>
+        <v>4.047653857846658</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.808676390120023</v>
+        <v>3.680455378684828</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.413495131644755</v>
+        <v>-5.326981858914779</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.642921913148373</v>
+        <v>1.549306210805169</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6552929224158626</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.201852143569541</v>
+        <v>4.073631132134346</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394115</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.755592136041195</v>
+        <v>3.627371124606</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.391122106037049</v>
+        <v>-5.304608833307073</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.598786869312627</v>
+        <v>1.505171166969423</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6665486735287641</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.155521340158454</v>
+        <v>4.027300328723259</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456732</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.94079034092655</v>
+        <v>3.812569329491355</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.424138401947793</v>
+        <v>-5.337625129217818</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.770778555833684</v>
+        <v>1.677162853490481</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5971112968620125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.299057119043757</v>
+        <v>4.170836107608562</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883682</v>
+        <v>3.713762536883683</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.932711566754799</v>
+        <v>3.804490555319604</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.412610766298185</v>
+        <v>-5.326097493568209</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.767310835921777</v>
+        <v>1.673695133578573</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6561119550633749</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.326378739792824</v>
+        <v>4.198157728357629</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236303</v>
+        <v>3.717150699236305</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.936379679276587</v>
+        <v>3.808158667841393</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.509952267640553</v>
+        <v>-5.423438994910578</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.732042347906618</v>
+        <v>1.638426645563415</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6116917728978866</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.303394743015319</v>
+        <v>4.175173731580125</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942769</v>
+        <v>3.705201079427692</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.937630761469426</v>
+        <v>3.809409750034231</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.59580829698052</v>
+        <v>-5.509295024250545</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.69895101836347</v>
+        <v>1.605335316020266</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5693157036717515</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.279220183672477</v>
+        <v>4.150999172237283</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.920049963289927</v>
+        <v>3.791828951854733</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.604645094396639</v>
+        <v>-5.518131821666664</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.677835501217524</v>
+        <v>1.584219798874321</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.257174081908168</v>
+        <v>4.128953070472974</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667459</v>
+        <v>3.715544411667461</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.930214474334977</v>
+        <v>3.801993462899783</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.696027656962098</v>
+        <v>-5.609514384232122</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.65144698723639</v>
+        <v>1.557831284893187</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.245399662121611</v>
+        <v>4.117178650686417</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889197</v>
+        <v>3.673978374889198</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.032342732159245</v>
+        <v>3.904121720724051</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.684320938975092</v>
+        <v>-5.597807666245116</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.75825793225546</v>
+        <v>1.664642229912257</v>
       </c>
       <c r="F2076" t="n">
         <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.354551950738083</v>
+        <v>4.226330939302889</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409572</v>
+        <v>3.682476099409573</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.03537507089065</v>
+        <v>3.907154059455455</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.755233012717369</v>
+        <v>-5.668719739987393</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.732925441489954</v>
+        <v>1.63930973914675</v>
       </c>
       <c r="F2077" t="n">
         <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.357584289469488</v>
+        <v>4.229363278034293</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.036193896622915</v>
+        <v>3.90797288518772</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.765549110883721</v>
+        <v>-5.679035838153745</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.729617827955678</v>
+        <v>1.636002125612474</v>
       </c>
       <c r="F2078" t="n">
         <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.358403115201752</v>
+        <v>4.230182103766557</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.770053391710332</v>
+        <v>3.623960959762294</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.035372563535004</v>
+        <v>3.907151552099809</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.855167298705535</v>
+        <v>-5.678941870136373</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.692949219739042</v>
+        <v>1.635218379731513</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5242565266745941</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.349926479539761</v>
+        <v>4.229582687487038</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.770053391710332</v>
+        <v>3.800870306884086</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.035372563535004</v>
+        <v>3.901383538044163</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.855167298705535</v>
+        <v>-5.822543034159758</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.692949219739042</v>
+        <v>1.572009900066512</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5242565266745941</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.349926479539761</v>
+        <v>4.223814673431391</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.657773650705921</v>
+        <v>3.671015692129649</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.035372563535004</v>
+        <v>3.901383538044163</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.854218875587496</v>
+        <v>-5.82159461104172</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.693328588986258</v>
+        <v>1.572389269313728</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5242565266745941</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.349926479539761</v>
+        <v>4.223814673431391</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.890931774628624</v>
+        <v>3.904173816052352</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.048100171516096</v>
+        <v>3.914111146025255</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.954488693546518</v>
+        <v>-5.92186442900074</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.665948269783741</v>
+        <v>1.545008950111212</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5242565266745941</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.362654087520853</v>
+        <v>4.236542281412484</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.726937566389768</v>
+        <v>3.740179607813496</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.050046169940484</v>
+        <v>3.916057144449643</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.948496446757706</v>
+        <v>-5.915872182211928</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.670291166923654</v>
+        <v>1.549351847251124</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5242565266745941</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.364600085945241</v>
+        <v>4.238488279836871</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.751808755114217</v>
+        <v>3.765050796537945</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.043700305958253</v>
+        <v>3.909711280467412</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.859938485626938</v>
+        <v>-5.827314221081161</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.69936848739373</v>
+        <v>1.5784291677212</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5242565266745941</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.358254221963009</v>
+        <v>4.23214241585464</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.745167129348089</v>
+        <v>3.758409170771817</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.043008983397248</v>
+        <v>3.909019957906407</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.842179408123864</v>
+        <v>-5.809555143578087</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.705780795833955</v>
+        <v>1.584841476161425</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5242565266745941</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.357562899402005</v>
+        <v>4.231451093293636</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.788098555685995</v>
+        <v>3.801340597109723</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.055791169305835</v>
+        <v>3.921802143814994</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.742549257074796</v>
+        <v>-5.709924992529019</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.758415042162169</v>
+        <v>1.637475722489639</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6238866777236616</v>
+        <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.430123175940032</v>
+        <v>4.304011369831663</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.785223505420269</v>
+        <v>3.798465546843998</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.244945434804562</v>
+        <v>4.110956409313721</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.791948765763808</v>
+        <v>-5.75932450121803</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.927809504185291</v>
+        <v>1.806870184512761</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6341455111554063</v>
+        <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.625432741497805</v>
+        <v>4.499320935389436</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.758944466928133</v>
+        <v>3.772186508351862</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.232134107907424</v>
+        <v>4.098145082416583</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.585264292121431</v>
+        <v>-5.552640027575654</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.997671966745103</v>
+        <v>1.876732647072574</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8408299847977819</v>
+        <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.736632098786093</v>
+        <v>4.610520292677724</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.750150797127543</v>
+        <v>3.763392838551272</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.234135621561529</v>
+        <v>4.100146596070688</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.619421187118958</v>
+        <v>-5.58679692257318</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.986010722400198</v>
+        <v>1.865071402727668</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7572462152569694</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.68848335071571</v>
+        <v>4.562371544607341</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.792348523617385</v>
+        <v>3.805590565041113</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.587632735551196</v>
+        <v>4.453643710060355</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.526831708057501</v>
+        <v>-5.494207443511724</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.376543628014448</v>
+        <v>2.255604308341918</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7572462152569694</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.041980464705378</v>
+        <v>4.915868658597009</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.818922313073676</v>
+        <v>3.832164354497404</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.592195847118299</v>
+        <v>4.458206821627458</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.599992311830646</v>
+        <v>-5.567368047284869</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.351842498072293</v>
+        <v>2.230903178399763</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7292250152227264</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.029730856251936</v>
+        <v>4.903619050143567</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.84506884906857</v>
+        <v>3.858310890492298</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.642025788441827</v>
+        <v>4.508036762950986</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.547776002034304</v>
+        <v>-5.515151737488527</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.422558963314357</v>
+        <v>2.301619643641828</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7292250152227264</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.079560797575463</v>
+        <v>4.953448991467093</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.831693555012751</v>
+        <v>3.844935596436479</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.650839758651838</v>
+        <v>4.516850733160997</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.49526867452381</v>
+        <v>-5.462644409978032</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.452375864528566</v>
+        <v>2.331436544856036</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7817323427332213</v>
+        <v>0.7948610417040077</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.11987916429177</v>
+        <v>4.993767358183401</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.835134824615761</v>
+        <v>3.848376866039489</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.646477342691035</v>
+        <v>4.512488317200193</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.51002399872395</v>
+        <v>-5.477399734178173</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.442111318887707</v>
+        <v>2.321171999215177</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7817323427332213</v>
+        <v>0.7948610417040077</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.115516748330967</v>
+        <v>4.989404942222598</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.854911074100755</v>
+        <v>3.868153115524484</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.637401846107315</v>
+        <v>4.503412820616473</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.460559375354038</v>
+        <v>-5.427935110808261</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.452821671651951</v>
+        <v>2.331882351979422</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.831196966103133</v>
+        <v>0.8443256650739194</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.136120025769195</v>
+        <v>5.010008219660826</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.694312199127948</v>
+        <v>3.849040239867957</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.633809513822249</v>
+        <v>4.499820488331408</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.303447198131892</v>
+        <v>-5.264827118654646</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.512074210255745</v>
+        <v>2.393533216555802</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.98830914332528</v>
+        <v>1.007433657227535</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.226794999817417</v>
+        <v>5.104280682667929</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.887600205048849</v>
+        <v>3.870204928232972</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.633809513822249</v>
+        <v>4.508867525022536</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.306197314121219</v>
+        <v>-5.244184027853418</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.510974163860014</v>
+        <v>2.410837489567422</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.98830914332528</v>
+        <v>1.007433657227535</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.226794999817417</v>
+        <v>5.113327719359057</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.872929713995553</v>
+        <v>3.855534437179676</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.634666978808371</v>
+        <v>4.509724990008658</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.368905230595777</v>
+        <v>-5.306891944327976</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.486748462256312</v>
+        <v>2.38661178796372</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9256012268507222</v>
+        <v>0.9447257407529769</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.190027714918804</v>
+        <v>5.076560434460444</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.9020831257836</v>
+        <v>3.884687848967723</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.597576395598723</v>
+        <v>4.47263440679901</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.320897106752084</v>
+        <v>-5.258883820484283</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.468861128584141</v>
+        <v>2.368724454291549</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9256012268507222</v>
+        <v>0.9447257407529769</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.152937131709156</v>
+        <v>5.039469851250796</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.912757633834491</v>
+        <v>3.895362357018614</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.601508649156672</v>
+        <v>4.47656666035696</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.242071449568494</v>
+        <v>-5.180058163300693</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.504323645015527</v>
+        <v>2.404186970722936</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.004426884034313</v>
+        <v>1.023551397936567</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.20416477957726</v>
+        <v>5.090697499118901</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.909006257891014</v>
+        <v>3.891610981075138</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.596407741763709</v>
+        <v>4.471465752963997</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.05013664831462</v>
+        <v>-4.988123362046819</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.575996658124113</v>
+        <v>2.475859983831522</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.004426884034313</v>
+        <v>1.023551397936567</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.199063872184297</v>
+        <v>5.085596591725938</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.889827770251324</v>
+        <v>3.872432493435448</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.591761651152805</v>
+        <v>4.466819662353092</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.931963270296693</v>
+        <v>-4.869949984028892</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.61861991872038</v>
+        <v>2.518483244427788</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.12260026205224</v>
+        <v>1.141724775954495</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.265321808384149</v>
+        <v>5.151854527925789</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.876967000733613</v>
+        <v>3.859571723917736</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.620850244015831</v>
+        <v>4.495908255216119</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.843116153437196</v>
+        <v>-4.781102867169395</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.683247358327205</v>
+        <v>2.583110684034614</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.211447378911738</v>
+        <v>1.230571892813992</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.347718671362874</v>
+        <v>5.234251390904515</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.802434493323078</v>
+        <v>3.828006274013642</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.614410467027009</v>
+        <v>4.489468478227296</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.803234567433103</v>
+        <v>-4.754053829476141</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.692760215740019</v>
+        <v>2.587490522123093</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.25132896491583</v>
+        <v>1.257620930507246</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.365207845976507</v>
+        <v>5.244041036531645</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.844656489456963</v>
+        <v>3.823987445263772</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.614410467027009</v>
+        <v>4.489468478227296</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.809267847619873</v>
+        <v>-4.760087109662911</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.690346903665311</v>
+        <v>2.585077210048385</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.25132896491583</v>
+        <v>1.257620930507246</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.365207845976507</v>
+        <v>5.244041036531645</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.836326247364036</v>
+        <v>3.815657203170846</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.618048634169421</v>
+        <v>4.493106645369709</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.861119623193034</v>
+        <v>-4.811938885236072</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.673244360578459</v>
+        <v>2.567974666961533</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.199477189342669</v>
+        <v>1.205769154934085</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.337734947775022</v>
+        <v>5.21656813833016</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,45 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.852568539043109</v>
+        <v>3.83058698643141</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.581540381353258</v>
+        <v>4.456598392553546</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.888177069324861</v>
+        <v>-4.838996331367899</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.625913129309565</v>
+        <v>2.520643435692639</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.199477189342669</v>
+        <v>1.205769154934085</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.301226694958859</v>
+        <v>5.180059885513997</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="2" t="n">
+        <v>45570</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>3.868704091943204</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>4.458006342300737</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>-4.962948765817973</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>2.472470411659801</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>1.176013484305617</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>5.163614432884108</v>
       </c>
     </row>
   </sheetData>
